--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="67.25" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1843건 (회사 기간 670건)</t>
+          <t>2025건 (회사 기간 670건)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>470건 (평일 야간·주말·휴가 시간 커밋)</t>
+          <t>477건 (평일 야간·주말·휴가 시간 커밋)</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>104 / 113개 (92%)</t>
+          <t>109 / 118개 (92%)</t>
         </is>
       </c>
     </row>
@@ -4117,13 +4117,209 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">  (9)</t>
+            <t xml:space="preserve">  (10)</t>
           </r>
         </is>
       </c>
     </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-09-28  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (15)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-09-29  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■■■■■■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (56)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-09-30  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (25)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-10-01  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (39)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-10-06  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (17)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-10-07  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (26)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-10-08  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (3)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="126">
+  <mergeCells count="133">
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A11:E11"/>
@@ -4144,18 +4340,22 @@
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A113:E113"/>
     <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A129:E129"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A91:E91"/>
+    <mergeCell ref="A131:E131"/>
     <mergeCell ref="A100:E100"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A63:E63"/>
     <mergeCell ref="A115:E115"/>
     <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A130:E130"/>
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A83:E83"/>
     <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A132:E132"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A119:E119"/>
     <mergeCell ref="A69:E69"/>
@@ -4163,6 +4363,7 @@
     <mergeCell ref="A118:E118"/>
     <mergeCell ref="A75:E75"/>
     <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A133:E133"/>
     <mergeCell ref="A80:E80"/>
     <mergeCell ref="A120:E120"/>
     <mergeCell ref="A55:E55"/>
@@ -4201,10 +4402,12 @@
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A47:E47"/>
     <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A135:E135"/>
     <mergeCell ref="A122:E122"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A125:E125"/>
     <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A134:E134"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A112:E112"/>
     <mergeCell ref="A121:E121"/>
@@ -4261,7 +4464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4833,7 +5036,31 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" ht="81" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-24 ~ 10-08</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>모바일·입출고·불량 개선</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>모바일 메뉴·대시보드·재고·입출고·불량·일보·출하·업무함 화면 개선
+원자재 사급·샘플 및 튜브 원자재 입출고 추가
+불량 사유 관리와 발생 통계 개선
+제출별 내역 묶음 및 취소·기간별 집계 개선
+직원별 화면 설정 동기화와 작업자 확인 안내</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -4847,7 +5074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7401,127 +7628,127 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="12" t="n">
+      <c r="A106" s="9" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="13" t="inlineStr">
-        <is>
-          <t>실 재고 데이터 입력 + 직원 테스트</t>
-        </is>
-      </c>
-      <c r="C106" s="12" t="inlineStr">
-        <is>
-          <t>데이터</t>
-        </is>
-      </c>
-      <c r="D106" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E106" s="13" t="inlineStr">
-        <is>
-          <t>BOM·입출고 정리 후</t>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>모바일 출하 업무</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>출하</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E106" s="10" t="inlineStr">
+        <is>
+          <t>요청 작성·수정·준비·픽업 처리와 이력 조회</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="12" t="n">
+      <c r="A107" s="9" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="13" t="inlineStr">
-        <is>
-          <t>불량 처리 흐름 Phase 2</t>
-        </is>
-      </c>
-      <c r="C107" s="12" t="inlineStr">
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>제출별 작업 내역 묶음</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>이력</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr">
+        <is>
+          <t>함께 제출한 작업 묶음과 개별 상세 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>불량 사유 관리</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
         <is>
           <t>생산</t>
         </is>
       </c>
-      <c r="D107" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E107" s="13" t="inlineStr">
-        <is>
-          <t>부서 결재·집계·자동화</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="12" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="13" t="inlineStr">
-        <is>
-          <t>역할별 접근 권한 연동</t>
-        </is>
-      </c>
-      <c r="C108" s="12" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="D108" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E108" s="13" t="inlineStr">
-        <is>
-          <t>부서·역할 기반 (PIN 로그인 완료)</t>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t>사유 검색·추가·수정·숨김·복원</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="12" t="n">
+      <c r="A109" s="9" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="13" t="inlineStr">
-        <is>
-          <t>총재고 / 가용재고 / 예약재고 분리</t>
-        </is>
-      </c>
-      <c r="C109" s="12" t="inlineStr">
-        <is>
-          <t>재고</t>
-        </is>
-      </c>
-      <c r="D109" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E109" s="13" t="inlineStr">
-        <is>
-          <t>재고 가용성 계산 고도화</t>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>불량 발생 통계 상세 분석</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t>기간 비교와 사유·부서·품목별 통계</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="12" t="n">
+      <c r="A110" s="9" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="13" t="inlineStr">
-        <is>
-          <t>외부 접근 환경 구성</t>
-        </is>
-      </c>
-      <c r="C110" s="12" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="D110" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E110" s="13" t="inlineStr">
-        <is>
-          <t>PC 또는 NAS 서버 + API 인증</t>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>튜브 원자재 입출고</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>입출고</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>전용 업체 구분·TR 원자재 입고와 업체 출고</t>
         </is>
       </c>
     </row>
@@ -7531,12 +7758,12 @@
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>발주 관리</t>
+          <t>실 재고 데이터 입력 + 직원 테스트</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="D111" s="14" t="inlineStr">
@@ -7544,7 +7771,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E111" s="13" t="inlineStr"/>
+      <c r="E111" s="13" t="inlineStr">
+        <is>
+          <t>BOM·입출고 정리 후</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="n">
@@ -7552,7 +7783,7 @@
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>생산 실적 / 원가 관리</t>
+          <t>불량 처리 흐름 Phase 2</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
@@ -7565,7 +7796,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E112" s="13" t="inlineStr"/>
+      <c r="E112" s="13" t="inlineStr">
+        <is>
+          <t>부서 결재·집계·자동화</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="12" t="n">
@@ -7573,12 +7808,12 @@
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>부서별 생산진행도 대시보드</t>
+          <t>역할별 접근 권한 연동</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D113" s="14" t="inlineStr">
@@ -7588,7 +7823,7 @@
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>사장님 요청 — 검토 중</t>
+          <t>부서·역할 기반 (PIN 로그인 완료)</t>
         </is>
       </c>
     </row>
@@ -7598,20 +7833,137 @@
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
+          <t>총재고 / 가용재고 / 예약재고 분리</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E114" s="13" t="inlineStr">
+        <is>
+          <t>재고 가용성 계산 고도화</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="13" t="inlineStr">
+        <is>
+          <t>외부 접근 환경 구성</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="D115" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="inlineStr">
+        <is>
+          <t>PC 또는 NAS 서버 + API 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="12" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="13" t="inlineStr">
+        <is>
+          <t>발주 관리</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E116" s="13" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>생산 실적 / 원가 관리</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D117" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E117" s="13" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="13" t="inlineStr">
+        <is>
+          <t>부서별 생산진행도 대시보드</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E118" s="13" t="inlineStr">
+        <is>
+          <t>사장님 요청 — 검토 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="13" t="inlineStr">
+        <is>
           <t>출하 거래처 관리</t>
         </is>
       </c>
-      <c r="C114" s="12" t="inlineStr">
+      <c r="C119" s="12" t="inlineStr">
         <is>
           <t>출하</t>
         </is>
       </c>
-      <c r="D114" s="14" t="inlineStr">
+      <c r="D119" s="14" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E114" s="13" t="inlineStr">
+      <c r="E119" s="13" t="inlineStr">
         <is>
           <t>거래처 마스터 + 출하 이력</t>
         </is>
@@ -7628,7 +7980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10439,7 +10791,7 @@
         </is>
       </c>
       <c r="B119" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
@@ -10451,6 +10803,172 @@
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="67.5" customHeight="1">
+      <c r="A120" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B120" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="C120" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-28 mes: 빈 일보 저장 허용
+2026-09-28 docs: 주간보고 9/12~9/23 갱신
+2026-09-28 ops: 프론트 런타임 사전검사와 동기화 안전성 보강
+2026-09-28 docs: 변경 위험에 따른 검증 범위 선택 지침 개선
+2026-09-28 dashboard: BOM 재고 구분과 로딩 표시 개선</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="67.5" customHeight="1">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 frontend: 출하 목록 정보 정리와 상세 수량 강조
+2026-09-29 frontend: 입출고 로그인 부서 우선 정렬 복구
+2026-09-29 defect: 불량 처리 선택 화면 통합 및 카드 배치 정리
+2026-09-29 frontend: 품목 전환 목록 누락과 선택 행 표시 수정
+2026-09-29 mobile: 공통 모바일 표시 범위와 화면별 스타일 추가</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="67.5" customHeight="1">
+      <c r="A122" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B122" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="C122" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30 frontend: 재고 상세 패널 스크롤바 위치 조정
+2026-09-30 mobile: 불량 처리 단계 헤더 통합
+2026-09-30 mobile: 불량 격리 목록과 필터 압축
+2026-09-30 mobile: 모바일 스크롤 프레임과 스크롤바 위치 조정
+2026-09-30 mobile: 모바일 셸 본문 상단 간격 조정</t>
+        </is>
+      </c>
+      <c r="D122" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="67.5" customHeight="1">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 fix: 일보 자동 저장 시 공백과 줄바꿈 보존
+2026-10-01 inventory: 불량·B급·구형 재고 표시 구분
+2026-10-01 mobile: 터치 화면의 스크롤바 색상 조정
+2026-10-01 mobile: 공통 스크롤 영역의 터치 여백 정리
+2026-10-01 mobile: 선택 메뉴의 항목 간격 스타일 추가</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="67.5" customHeight="1">
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B124" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="C124" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-06 mobile: 대시보드 가독성 개선 및 BOM 조회 연결
+2026-10-06 defect: 격리 묶음 행 전체 클릭으로 기록 펼침
+2026-10-06 frontend: PC·모바일 알림 읽음 동기화 개선
+2026-10-06 defect: 불량 묶음 행 전체 클릭 펼침 적용
+2026-10-06 mobile: 대시보드와 체크리스트 디자인 및 모바일 정렬 개선</t>
+        </is>
+      </c>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="67.5" customHeight="1">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07 mobile: 출하 업무 확장과 전체 화면 디자인 통일
+2026-10-07 frontend: 번들 크기 예산을 2.95 MB로 조정
+2026-10-07 qa: 화면 변경에 맞춰 CI 회귀 테스트 수정
+2026-10-07 docs: 플랜 기본 추천 모델을 GPT-6.1 Sol로 갱신
+2026-10-07 mobile: 공통 헤더와 재진입·복귀 동작 및 스크롤 경계 통일</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40.5" customHeight="1">
+      <c r="A126" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B126" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C126" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-08 io: 튜브 원자재 입출고 및 전용 업체 관리 추가
+2026-10-08 test: 마이그레이션 최신 버전 기대값 갱신
+2026-10-08 ops: 배포 정지 중 감시 프로세스 재기동 방지</t>
+        </is>
+      </c>
+      <c r="D126" s="15" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
@@ -10467,7 +10985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1844"/>
+  <dimension ref="A1:F2026"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -69486,6 +70004,5830 @@
         </is>
       </c>
     </row>
+    <row r="1845">
+      <c r="A1845" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1845" s="7" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="C1845" s="7" t="inlineStr">
+        <is>
+          <t>ae8c05fe</t>
+        </is>
+      </c>
+      <c r="D1845" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-23 frontend: 일보 이미지 책 방향과 눈 모양 수정</t>
+        </is>
+      </c>
+      <c r="E1845" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1845" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1846" s="15" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="C1846" s="15" t="inlineStr">
+        <is>
+          <t>4fc743b2</t>
+        </is>
+      </c>
+      <c r="D1846" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-28 mes: 빈 일보 저장 허용</t>
+        </is>
+      </c>
+      <c r="E1846" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1846" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1847" s="7" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="C1847" s="7" t="inlineStr">
+        <is>
+          <t>65a6736a</t>
+        </is>
+      </c>
+      <c r="D1847" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28 docs: 주간보고 9/12~9/23 갱신</t>
+        </is>
+      </c>
+      <c r="E1847" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1847" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1848" s="15" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="C1848" s="15" t="inlineStr">
+        <is>
+          <t>edcccf04</t>
+        </is>
+      </c>
+      <c r="D1848" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-28 ops: 프론트 런타임 사전검사와 동기화 안전성 보강</t>
+        </is>
+      </c>
+      <c r="E1848" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1848" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1849" s="7" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="C1849" s="7" t="inlineStr">
+        <is>
+          <t>25527dca</t>
+        </is>
+      </c>
+      <c r="D1849" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28 docs: 변경 위험에 따른 검증 범위 선택 지침 개선</t>
+        </is>
+      </c>
+      <c r="E1849" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1849" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1850" s="15" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="C1850" s="15" t="inlineStr">
+        <is>
+          <t>8bb6a036</t>
+        </is>
+      </c>
+      <c r="D1850" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-28 dashboard: BOM 재고 구분과 로딩 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1850" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1850" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1851" s="7" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="C1851" s="7" t="inlineStr">
+        <is>
+          <t>bc4700a5</t>
+        </is>
+      </c>
+      <c r="D1851" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28 warehouse: 원자재 입출고 확장 및 이력 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1851" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1851" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1852" s="15" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="C1852" s="15" t="inlineStr">
+        <is>
+          <t>f5b15a70</t>
+        </is>
+      </c>
+      <c r="D1852" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-28 warehouse: 입출고 선택 카드와 이미지 로딩 및 뒤로가기 개선</t>
+        </is>
+      </c>
+      <c r="E1852" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1852" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1853" s="7" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="C1853" s="7" t="inlineStr">
+        <is>
+          <t>c7615e52</t>
+        </is>
+      </c>
+      <c r="D1853" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28 frontend: 일보 파란 책 표지 이미지 적용</t>
+        </is>
+      </c>
+      <c r="E1853" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1853" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1854" s="15" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C1854" s="15" t="inlineStr">
+        <is>
+          <t>913ab33a</t>
+        </is>
+      </c>
+      <c r="D1854" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-28 frontend: 이력 문구와 대시보드·이력 헤더 테두리 개선</t>
+        </is>
+      </c>
+      <c r="E1854" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1854" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1855" s="7" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="C1855" s="7" t="inlineStr">
+        <is>
+          <t>cec950af</t>
+        </is>
+      </c>
+      <c r="D1855" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28 warehouse: 원자재 초안 저장과 입출고 방향 색상 정리</t>
+        </is>
+      </c>
+      <c r="E1855" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1855" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1856" s="15" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="C1856" s="15" t="inlineStr">
+        <is>
+          <t>ca5d5376</t>
+        </is>
+      </c>
+      <c r="D1856" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-28 frontend: 공급처 정렬 개선과 덱스레이 이미지 보존</t>
+        </is>
+      </c>
+      <c r="E1856" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1856" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1857" s="7" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="C1857" s="7" t="inlineStr">
+        <is>
+          <t>5c48ed07</t>
+        </is>
+      </c>
+      <c r="D1857" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28 frontend: 입출고 수량 조정 위치 표시 통일</t>
+        </is>
+      </c>
+      <c r="E1857" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1857" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1858" s="15" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="C1858" s="15" t="inlineStr">
+        <is>
+          <t>8950be8c</t>
+        </is>
+      </c>
+      <c r="D1858" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-28 frontend: 최근 내역 가독성과 입출고 선택 화면 개선</t>
+        </is>
+      </c>
+      <c r="E1858" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1858" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1859" s="7" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="C1859" s="7" t="inlineStr">
+        <is>
+          <t>50549c4d</t>
+        </is>
+      </c>
+      <c r="D1859" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28 frontend: AS·연구 출고 색상과 차감 위치 정렬 통일</t>
+        </is>
+      </c>
+      <c r="E1859" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1859" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1860" s="19" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="C1860" s="19" t="inlineStr">
+        <is>
+          <t>ac92db97</t>
+        </is>
+      </c>
+      <c r="D1860" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-28 frontend: AS·연구 선택 카드에 덱스레이 이미지 적용</t>
+        </is>
+      </c>
+      <c r="E1860" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1860" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1861" s="7" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="C1861" s="7" t="inlineStr">
+        <is>
+          <t>bf19d31d</t>
+        </is>
+      </c>
+      <c r="D1861" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 frontend: 출하 목록 정보 정리와 상세 수량 강조</t>
+        </is>
+      </c>
+      <c r="E1861" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1861" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1862" s="15" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C1862" s="15" t="inlineStr">
+        <is>
+          <t>2dbe1519</t>
+        </is>
+      </c>
+      <c r="D1862" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 frontend: 입출고 로그인 부서 우선 정렬 복구</t>
+        </is>
+      </c>
+      <c r="E1862" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1862" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1863" s="7" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="C1863" s="7" t="inlineStr">
+        <is>
+          <t>8eb884b6</t>
+        </is>
+      </c>
+      <c r="D1863" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 defect: 불량 처리 선택 화면 통합 및 카드 배치 정리</t>
+        </is>
+      </c>
+      <c r="E1863" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1863" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1864" s="15" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="C1864" s="15" t="inlineStr">
+        <is>
+          <t>4ee96514</t>
+        </is>
+      </c>
+      <c r="D1864" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 frontend: 품목 전환 목록 누락과 선택 행 표시 수정</t>
+        </is>
+      </c>
+      <c r="E1864" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1864" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1865" s="7" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="C1865" s="7" t="inlineStr">
+        <is>
+          <t>75d89e8d</t>
+        </is>
+      </c>
+      <c r="D1865" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 mobile: 공통 모바일 표시 범위와 화면별 스타일 추가</t>
+        </is>
+      </c>
+      <c r="E1865" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1865" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1866" s="15" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="C1866" s="15" t="inlineStr">
+        <is>
+          <t>6c4f338a</t>
+        </is>
+      </c>
+      <c r="D1866" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 mobile: 공통 표시 범위와 스크롤·하단 영역 정리</t>
+        </is>
+      </c>
+      <c r="E1866" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1866" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1867" s="7" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="C1867" s="7" t="inlineStr">
+        <is>
+          <t>dcca7a33</t>
+        </is>
+      </c>
+      <c r="D1867" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 mobile: 모바일 값 스켈레톤과 데이터 표시 모션 추가</t>
+        </is>
+      </c>
+      <c r="E1867" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1867" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1868" s="15" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="C1868" s="15" t="inlineStr">
+        <is>
+          <t>b22ec0cc</t>
+        </is>
+      </c>
+      <c r="D1868" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 mobile: 화면별 스켈레톤과 조회 상태 공통 기반 추가</t>
+        </is>
+      </c>
+      <c r="E1868" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1868" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1869" s="7" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C1869" s="7" t="inlineStr">
+        <is>
+          <t>6969569f</t>
+        </is>
+      </c>
+      <c r="D1869" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 mobile: 로그인 화면 표시와 입력 간격 개선</t>
+        </is>
+      </c>
+      <c r="E1869" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1869" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1870" s="15" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C1870" s="15" t="inlineStr">
+        <is>
+          <t>a17f5bc7</t>
+        </is>
+      </c>
+      <c r="D1870" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 mobile: 모바일 알림 패널과 펼침 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1870" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1870" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1871" s="7" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C1871" s="7" t="inlineStr">
+        <is>
+          <t>c213ac0d</t>
+        </is>
+      </c>
+      <c r="D1871" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 mobile: 알림 표시와 펼침 패널 정리</t>
+        </is>
+      </c>
+      <c r="E1871" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1871" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1872" s="15" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C1872" s="15" t="inlineStr">
+        <is>
+          <t>e36c5f5d</t>
+        </is>
+      </c>
+      <c r="D1872" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 inventory: 모바일 BOM 트리 들여쓰기와 펼침·조회 상태 개선</t>
+        </is>
+      </c>
+      <c r="E1872" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1872" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1873" s="7" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C1873" s="7" t="inlineStr">
+        <is>
+          <t>6deaa856</t>
+        </is>
+      </c>
+      <c r="D1873" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 inventory: BOM 상세 팝업과 깊은 구성 트리 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1873" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1873" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1874" s="15" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C1874" s="15" t="inlineStr">
+        <is>
+          <t>d4707813</t>
+        </is>
+      </c>
+      <c r="D1874" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 inventory: 모바일 재고 위치별 수량 표시 정리</t>
+        </is>
+      </c>
+      <c r="E1874" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1874" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1875" s="7" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C1875" s="7" t="inlineStr">
+        <is>
+          <t>185d5bc9</t>
+        </is>
+      </c>
+      <c r="D1875" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 inventory: 모바일 재고 상세와 위치·예약 조회 상태 개선</t>
+        </is>
+      </c>
+      <c r="E1875" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1875" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1876" s="15" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C1876" s="15" t="inlineStr">
+        <is>
+          <t>b755c7db</t>
+        </is>
+      </c>
+      <c r="D1876" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 capacity: 모바일 생산 가능수량 요약 패널 개선</t>
+        </is>
+      </c>
+      <c r="E1876" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1876" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1877" s="7" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C1877" s="7" t="inlineStr">
+        <is>
+          <t>6a522915</t>
+        </is>
+      </c>
+      <c r="D1877" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 capacity: 생산 가능수량 모바일 요약과 상세 조회 개선</t>
+        </is>
+      </c>
+      <c r="E1877" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1877" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1878" s="15" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C1878" s="15" t="inlineStr">
+        <is>
+          <t>9bc13249</t>
+        </is>
+      </c>
+      <c r="D1878" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 inventory: 모바일 재고 KPI 배치와 로딩 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1878" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1878" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1879" s="7" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C1879" s="7" t="inlineStr">
+        <is>
+          <t>1247b0cf</t>
+        </is>
+      </c>
+      <c r="D1879" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 inventory: 모바일 재고 행의 품명·수량·재고 분포 개선</t>
+        </is>
+      </c>
+      <c r="E1879" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1879" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1880" s="15" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C1880" s="15" t="inlineStr">
+        <is>
+          <t>9c7a27d1</t>
+        </is>
+      </c>
+      <c r="D1880" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 inventory: 모바일 재고 표와 순차 렌더링·로딩 상태 개선</t>
+        </is>
+      </c>
+      <c r="E1880" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1880" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1881" s="7" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C1881" s="7" t="inlineStr">
+        <is>
+          <t>0dae34fe</t>
+        </is>
+      </c>
+      <c r="D1881" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 inventory: 대시보드 재고 표와 KPI·목록 로딩 개선</t>
+        </is>
+      </c>
+      <c r="E1881" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1881" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1882" s="15" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C1882" s="15" t="inlineStr">
+        <is>
+          <t>dc65bf5a</t>
+        </is>
+      </c>
+      <c r="D1882" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 warehouse: 모바일 업무함 메뉴와 승인함 탭 정리</t>
+        </is>
+      </c>
+      <c r="E1882" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1882" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1883" s="7" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C1883" s="7" t="inlineStr">
+        <is>
+          <t>bd502140</t>
+        </is>
+      </c>
+      <c r="D1883" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 warehouse: 모바일 인수인계 목록과 조회 상태 개선</t>
+        </is>
+      </c>
+      <c r="E1883" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1883" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1884" s="15" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C1884" s="15" t="inlineStr">
+        <is>
+          <t>e834df6c</t>
+        </is>
+      </c>
+      <c r="D1884" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 warehouse: 모바일 초안 목록과 작성 탭 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1884" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1884" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1885" s="7" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C1885" s="7" t="inlineStr">
+        <is>
+          <t>94a4e78a</t>
+        </is>
+      </c>
+      <c r="D1885" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 warehouse: 모바일 업무함·승인함·인수인계 조회 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1885" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1885" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1886" s="15" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C1886" s="15" t="inlineStr">
+        <is>
+          <t>50eb5361</t>
+        </is>
+      </c>
+      <c r="D1886" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 warehouse: 모바일 공급업체 선택 목록과 로딩 개선</t>
+        </is>
+      </c>
+      <c r="E1886" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1886" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1887" s="7" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C1887" s="7" t="inlineStr">
+        <is>
+          <t>eb765a88</t>
+        </is>
+      </c>
+      <c r="D1887" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 warehouse: 입출고 작업·방향·공급업체 선택 화면 개선</t>
+        </is>
+      </c>
+      <c r="E1887" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1887" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1888" s="15" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C1888" s="15" t="inlineStr">
+        <is>
+          <t>2efd46c6</t>
+        </is>
+      </c>
+      <c r="D1888" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 warehouse: 모바일 품목 선택 영역과 조회 상태 개선</t>
+        </is>
+      </c>
+      <c r="E1888" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1888" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1889" s="7" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C1889" s="7" t="inlineStr">
+        <is>
+          <t>b16fa180</t>
+        </is>
+      </c>
+      <c r="D1889" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 warehouse: 모바일 수량 입력과 화살표 반복 조정 추가</t>
+        </is>
+      </c>
+      <c r="E1889" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1889" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1890" s="15" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C1890" s="15" t="inlineStr">
+        <is>
+          <t>a95e38ce</t>
+        </is>
+      </c>
+      <c r="D1890" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 warehouse: 모바일 묶음·구성품 행과 수량 표시 정리</t>
+        </is>
+      </c>
+      <c r="E1890" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1890" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1891" s="7" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C1891" s="7" t="inlineStr">
+        <is>
+          <t>15438023</t>
+        </is>
+      </c>
+      <c r="D1891" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 warehouse: 품목·묶음·수량 입력과 확인 화면 개선</t>
+        </is>
+      </c>
+      <c r="E1891" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1891" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1892" s="15" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C1892" s="15" t="inlineStr">
+        <is>
+          <t>5347c10b</t>
+        </is>
+      </c>
+      <c r="D1892" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 warehouse: 모바일 입출고 화면과 업무함 연결 정리</t>
+        </is>
+      </c>
+      <c r="E1892" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1892" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1893" s="7" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C1893" s="7" t="inlineStr">
+        <is>
+          <t>90d12e50</t>
+        </is>
+      </c>
+      <c r="D1893" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 defect: 모바일 불량 통계 조회와 KPI 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1893" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1893" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1894" s="15" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C1894" s="15" t="inlineStr">
+        <is>
+          <t>4d82fbd9</t>
+        </is>
+      </c>
+      <c r="D1894" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 defect: 불량 허브·보관·통계와 분해 로딩 개선</t>
+        </is>
+      </c>
+      <c r="E1894" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1894" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1895" s="7" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C1895" s="7" t="inlineStr">
+        <is>
+          <t>efda2c26</t>
+        </is>
+      </c>
+      <c r="D1895" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 defect: 모바일 불량 품목 선택 목록과 스크롤 개선</t>
+        </is>
+      </c>
+      <c r="E1895" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1895" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1896" s="15" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C1896" s="15" t="inlineStr">
+        <is>
+          <t>cec6efe1</t>
+        </is>
+      </c>
+      <c r="D1896" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 defect: 모바일 불량 처리·품목 선택 흐름 개선</t>
+        </is>
+      </c>
+      <c r="E1896" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1896" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1897" s="7" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C1897" s="7" t="inlineStr">
+        <is>
+          <t>852d91ce</t>
+        </is>
+      </c>
+      <c r="D1897" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 history: 모바일 내역 상세와 재고 변화 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1897" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1897" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1898" s="15" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C1898" s="15" t="inlineStr">
+        <is>
+          <t>51bc107a</t>
+        </is>
+      </c>
+      <c r="D1898" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 history: 모바일 내역 조회 대상 전환과 캐시 상태 보존</t>
+        </is>
+      </c>
+      <c r="E1898" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1898" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1899" s="7" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C1899" s="7" t="inlineStr">
+        <is>
+          <t>3a63cb5b</t>
+        </is>
+      </c>
+      <c r="D1899" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 history: 내역 필터·목록·조회 대상별 상태 개선</t>
+        </is>
+      </c>
+      <c r="E1899" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1899" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1900" s="15" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C1900" s="15" t="inlineStr">
+        <is>
+          <t>782e6493</t>
+        </is>
+      </c>
+      <c r="D1900" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 shipping: 모바일 출하 준비 목록과 단계 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1900" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1900" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1901" s="7" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C1901" s="7" t="inlineStr">
+        <is>
+          <t>4beacc1c</t>
+        </is>
+      </c>
+      <c r="D1901" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 daily: 모바일 일보 날짜·활동·편집 영역 정리</t>
+        </is>
+      </c>
+      <c r="E1901" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1901" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1902" s="15" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C1902" s="15" t="inlineStr">
+        <is>
+          <t>b7df9166</t>
+        </is>
+      </c>
+      <c r="D1902" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 daily: 모바일 일일 작업 일보 표시와 날짜별 로딩 개선</t>
+        </is>
+      </c>
+      <c r="E1902" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1902" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1903" s="7" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="C1903" s="7" t="inlineStr">
+        <is>
+          <t>ab340aaf</t>
+        </is>
+      </c>
+      <c r="D1903" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 assembly: 모바일 조립 체크리스트와 조회 상태 개선</t>
+        </is>
+      </c>
+      <c r="E1903" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1903" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1904" s="15" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="C1904" s="15" t="inlineStr">
+        <is>
+          <t>841a2af7</t>
+        </is>
+      </c>
+      <c r="D1904" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 mobile: 더보기·창고지도·주간보고 외곽 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1904" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1904" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1905" s="7" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="C1905" s="7" t="inlineStr">
+        <is>
+          <t>b3fe76a0</t>
+        </is>
+      </c>
+      <c r="D1905" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 mobile: 셸 조회 상태와 탭 아이콘·계정 메뉴 통합</t>
+        </is>
+      </c>
+      <c r="E1905" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1905" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1906" s="15" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="C1906" s="15" t="inlineStr">
+        <is>
+          <t>ff4b43fd</t>
+        </is>
+      </c>
+      <c r="D1906" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 docs: 모바일 UI 보존 기준과 초기 실행 기록 보관</t>
+        </is>
+      </c>
+      <c r="E1906" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1906" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1907" s="7" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="C1907" s="7" t="inlineStr">
+        <is>
+          <t>65616712</t>
+        </is>
+      </c>
+      <c r="D1907" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 docs: 모바일 UI 초기 검증 기록 보관</t>
+        </is>
+      </c>
+      <c r="E1907" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1907" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1908" s="15" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="C1908" s="15" t="inlineStr">
+        <is>
+          <t>5339fcde</t>
+        </is>
+      </c>
+      <c r="D1908" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 docs: 모바일 UI 폭 경계와 PC 비교 검증 기록 보관</t>
+        </is>
+      </c>
+      <c r="E1908" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1908" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1909" s="7" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="C1909" s="7" t="inlineStr">
+        <is>
+          <t>032b441f</t>
+        </is>
+      </c>
+      <c r="D1909" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 docs: 모바일 UI 사용자 피드백 반영 기록 보관</t>
+        </is>
+      </c>
+      <c r="E1909" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1909" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1910" s="15" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="C1910" s="15" t="inlineStr">
+        <is>
+          <t>42665731</t>
+        </is>
+      </c>
+      <c r="D1910" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 docs: 모바일 UI 추가 주석 반영 기록 보관</t>
+        </is>
+      </c>
+      <c r="E1910" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1910" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1911" s="7" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="C1911" s="7" t="inlineStr">
+        <is>
+          <t>b00b150d</t>
+        </is>
+      </c>
+      <c r="D1911" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 docs: 모바일 UI 후속 주석 반영 기록 보관</t>
+        </is>
+      </c>
+      <c r="E1911" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1911" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1912" s="15" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="C1912" s="15" t="inlineStr">
+        <is>
+          <t>20b600ab</t>
+        </is>
+      </c>
+      <c r="D1912" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 docs: 모바일 UI 후속 화면 검증 기록 보관</t>
+        </is>
+      </c>
+      <c r="E1912" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1912" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1913" s="7" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="C1913" s="7" t="inlineStr">
+        <is>
+          <t>75ca81c8</t>
+        </is>
+      </c>
+      <c r="D1913" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 docs: 모바일 스크롤과 모서리 검증 기록 보관</t>
+        </is>
+      </c>
+      <c r="E1913" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1913" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1914" s="15" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="C1914" s="15" t="inlineStr">
+        <is>
+          <t>3ccdce52</t>
+        </is>
+      </c>
+      <c r="D1914" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-29 docs: 모바일 스켈레톤 적용과 회귀 검증 기록 보관</t>
+        </is>
+      </c>
+      <c r="E1914" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1914" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1915" s="7" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="C1915" s="7" t="inlineStr">
+        <is>
+          <t>ce471f0f</t>
+        </is>
+      </c>
+      <c r="D1915" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-29 docs: 모바일 메인 통합 검증과 서버 보존 기록</t>
+        </is>
+      </c>
+      <c r="E1915" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F1915" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1916" s="15" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="C1916" s="15" t="inlineStr">
+        <is>
+          <t>d9cec919</t>
+        </is>
+      </c>
+      <c r="D1916" s="16" t="inlineStr">
+        <is>
+          <t>Merge branch 'codex/mobile-ui'</t>
+        </is>
+      </c>
+      <c r="E1916" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1916" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1917" s="7" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="C1917" s="7" t="inlineStr">
+        <is>
+          <t>ca891c91</t>
+        </is>
+      </c>
+      <c r="D1917" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30 frontend: 재고 상세 패널 스크롤바 위치 조정</t>
+        </is>
+      </c>
+      <c r="E1917" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1917" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1918" s="15" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="C1918" s="15" t="inlineStr">
+        <is>
+          <t>5afb57c4</t>
+        </is>
+      </c>
+      <c r="D1918" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 불량 처리 단계 헤더 통합</t>
+        </is>
+      </c>
+      <c r="E1918" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1918" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1919" s="7" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="C1919" s="7" t="inlineStr">
+        <is>
+          <t>63c603fe</t>
+        </is>
+      </c>
+      <c r="D1919" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 불량 격리 목록과 필터 압축</t>
+        </is>
+      </c>
+      <c r="E1919" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1919" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1920" s="15" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C1920" s="15" t="inlineStr">
+        <is>
+          <t>a5eed26a</t>
+        </is>
+      </c>
+      <c r="D1920" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 스크롤 프레임과 스크롤바 위치 조정</t>
+        </is>
+      </c>
+      <c r="E1920" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1920" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1921" s="7" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C1921" s="7" t="inlineStr">
+        <is>
+          <t>ee32ac1d</t>
+        </is>
+      </c>
+      <c r="D1921" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 셸 본문 상단 간격 조정</t>
+        </is>
+      </c>
+      <c r="E1921" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1921" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1922" s="15" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C1922" s="15" t="inlineStr">
+        <is>
+          <t>bca6a270</t>
+        </is>
+      </c>
+      <c r="D1922" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 대시보드 스크롤 구조 정리</t>
+        </is>
+      </c>
+      <c r="E1922" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1922" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1923" s="7" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C1923" s="7" t="inlineStr">
+        <is>
+          <t>b9984b20</t>
+        </is>
+      </c>
+      <c r="D1923" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 재고 목록 모서리와 로딩 표시 정리</t>
+        </is>
+      </c>
+      <c r="E1923" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1923" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1924" s="15" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C1924" s="15" t="inlineStr">
+        <is>
+          <t>690d8407</t>
+        </is>
+      </c>
+      <c r="D1924" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 재고 상세 수량과 위치 표시 조정</t>
+        </is>
+      </c>
+      <c r="E1924" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1924" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1925" s="7" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C1925" s="7" t="inlineStr">
+        <is>
+          <t>e1717968</t>
+        </is>
+      </c>
+      <c r="D1925" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 내역 검색과 필터 배치 조정</t>
+        </is>
+      </c>
+      <c r="E1925" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1925" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1926" s="15" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C1926" s="15" t="inlineStr">
+        <is>
+          <t>1a155eb6</t>
+        </is>
+      </c>
+      <c r="D1926" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 내역 화면 스크롤 프레임 적용</t>
+        </is>
+      </c>
+      <c r="E1926" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1926" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1927" s="7" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C1927" s="7" t="inlineStr">
+        <is>
+          <t>c18e64ba</t>
+        </is>
+      </c>
+      <c r="D1927" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 일일 작업 일보 스크롤 구조 정리</t>
+        </is>
+      </c>
+      <c r="E1927" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1927" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1928" s="15" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C1928" s="15" t="inlineStr">
+        <is>
+          <t>cec71f0e</t>
+        </is>
+      </c>
+      <c r="D1928" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 출하 화면 스크롤 프레임 적용</t>
+        </is>
+      </c>
+      <c r="E1928" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1928" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1929" s="7" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C1929" s="7" t="inlineStr">
+        <is>
+          <t>bc53577d</t>
+        </is>
+      </c>
+      <c r="D1929" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 창고지도 하단 여백 조정</t>
+        </is>
+      </c>
+      <c r="E1929" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1929" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1930" s="15" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C1930" s="15" t="inlineStr">
+        <is>
+          <t>79545e21</t>
+        </is>
+      </c>
+      <c r="D1930" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 조립 체크리스트 스크롤 구조 정리</t>
+        </is>
+      </c>
+      <c r="E1930" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1930" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1931" s="7" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C1931" s="7" t="inlineStr">
+        <is>
+          <t>4a294b0a</t>
+        </is>
+      </c>
+      <c r="D1931" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 불량 품목 선택 스크롤 표시 조정</t>
+        </is>
+      </c>
+      <c r="E1931" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1931" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1932" s="15" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="C1932" s="15" t="inlineStr">
+        <is>
+          <t>9eb6f557</t>
+        </is>
+      </c>
+      <c r="D1932" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 확인창 너비 조정</t>
+        </is>
+      </c>
+      <c r="E1932" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1932" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1933" s="7" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="C1933" s="7" t="inlineStr">
+        <is>
+          <t>a2af02bf</t>
+        </is>
+      </c>
+      <c r="D1933" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 입출고 품목 목록 스크롤 표시 조정</t>
+        </is>
+      </c>
+      <c r="E1933" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1933" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1934" s="15" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="C1934" s="15" t="inlineStr">
+        <is>
+          <t>06762ecb</t>
+        </is>
+      </c>
+      <c r="D1934" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 공급업체 목록 스크롤 프레임 적용</t>
+        </is>
+      </c>
+      <c r="E1934" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1934" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1935" s="7" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="C1935" s="7" t="inlineStr">
+        <is>
+          <t>56cb2650</t>
+        </is>
+      </c>
+      <c r="D1935" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 입출고 수량 카트 스크롤과 행 배치 조정</t>
+        </is>
+      </c>
+      <c r="E1935" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1935" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1936" s="15" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="C1936" s="15" t="inlineStr">
+        <is>
+          <t>6f6ff7ed</t>
+        </is>
+      </c>
+      <c r="D1936" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 입출고 방향 선택 그림 카드 적용</t>
+        </is>
+      </c>
+      <c r="E1936" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1936" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1937" s="7" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="C1937" s="7" t="inlineStr">
+        <is>
+          <t>16f0f53c</t>
+        </is>
+      </c>
+      <c r="D1937" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 입출고 작업 유형과 사용 부서 선택 정리</t>
+        </is>
+      </c>
+      <c r="E1937" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1937" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1938" s="15" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="C1938" s="15" t="inlineStr">
+        <is>
+          <t>03778b38</t>
+        </is>
+      </c>
+      <c r="D1938" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 입출고 단일 조정 폼을 통합 선택 흐름으로 전환</t>
+        </is>
+      </c>
+      <c r="E1938" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1938" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1939" s="7" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="C1939" s="7" t="inlineStr">
+        <is>
+          <t>28c3d18e</t>
+        </is>
+      </c>
+      <c r="D1939" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 모바일 스크롤 모서리 검증 기록 갱신</t>
+        </is>
+      </c>
+      <c r="E1939" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1939" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1940" s="15" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C1940" s="15" t="inlineStr">
+        <is>
+          <t>c42e8c19</t>
+        </is>
+      </c>
+      <c r="D1940" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-30 mobile: 불량 반품 공급업체 제목 테스트 갱신</t>
+        </is>
+      </c>
+      <c r="E1940" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1940" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1941" s="7" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="C1941" s="7" t="inlineStr">
+        <is>
+          <t>8501a847</t>
+        </is>
+      </c>
+      <c r="D1941" s="8" t="inlineStr">
+        <is>
+          <t>Merge branch 'codex/mobile-ui'</t>
+        </is>
+      </c>
+      <c r="E1941" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1941" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1942" s="15" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="C1942" s="15" t="inlineStr">
+        <is>
+          <t>ecff6d88</t>
+        </is>
+      </c>
+      <c r="D1942" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 fix: 일보 자동 저장 시 공백과 줄바꿈 보존</t>
+        </is>
+      </c>
+      <c r="E1942" s="15" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="F1942" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1943" s="7" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="C1943" s="7" t="inlineStr">
+        <is>
+          <t>0e44daa9</t>
+        </is>
+      </c>
+      <c r="D1943" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 inventory: 불량·B급·구형 재고 표시 구분</t>
+        </is>
+      </c>
+      <c r="E1943" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1943" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1944" s="15" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1944" s="15" t="inlineStr">
+        <is>
+          <t>d7942409</t>
+        </is>
+      </c>
+      <c r="D1944" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 터치 화면의 스크롤바 색상 조정</t>
+        </is>
+      </c>
+      <c r="E1944" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1944" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1945" s="7" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1945" s="7" t="inlineStr">
+        <is>
+          <t>4bcf8366</t>
+        </is>
+      </c>
+      <c r="D1945" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 공통 스크롤 영역의 터치 여백 정리</t>
+        </is>
+      </c>
+      <c r="E1945" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1945" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1946" s="15" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1946" s="15" t="inlineStr">
+        <is>
+          <t>12c42351</t>
+        </is>
+      </c>
+      <c r="D1946" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 선택 메뉴의 항목 간격 스타일 추가</t>
+        </is>
+      </c>
+      <c r="E1946" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1946" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1947" s="7" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1947" s="7" t="inlineStr">
+        <is>
+          <t>cc3f961b</t>
+        </is>
+      </c>
+      <c r="D1947" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 더보기 메뉴의 선택 항목 표시 정리</t>
+        </is>
+      </c>
+      <c r="E1947" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1947" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1948" s="15" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1948" s="15" t="inlineStr">
+        <is>
+          <t>500279af</t>
+        </is>
+      </c>
+      <c r="D1948" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 입출고 작업 종류 선택 간격 정리</t>
+        </is>
+      </c>
+      <c r="E1948" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1948" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1949" s="7" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1949" s="7" t="inlineStr">
+        <is>
+          <t>4aa2ecb5</t>
+        </is>
+      </c>
+      <c r="D1949" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 입출고 품목 선택 영역의 반응형 스크롤 적용</t>
+        </is>
+      </c>
+      <c r="E1949" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1949" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1950" s="15" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1950" s="15" t="inlineStr">
+        <is>
+          <t>00880647</t>
+        </is>
+      </c>
+      <c r="D1950" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 거래처 선택 영역에 공통 스크롤 적용</t>
+        </is>
+      </c>
+      <c r="E1950" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1950" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1951" s="7" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1951" s="7" t="inlineStr">
+        <is>
+          <t>d2ddf06c</t>
+        </is>
+      </c>
+      <c r="D1951" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 동반 품목 장바구니의 스크롤 영역 통일</t>
+        </is>
+      </c>
+      <c r="E1951" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1951" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1952" s="15" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1952" s="15" t="inlineStr">
+        <is>
+          <t>7641e091</t>
+        </is>
+      </c>
+      <c r="D1952" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 입출고 수량 입력과 하단 버튼 간격 조정</t>
+        </is>
+      </c>
+      <c r="E1952" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1952" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1953" s="7" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1953" s="7" t="inlineStr">
+        <is>
+          <t>f30152ef</t>
+        </is>
+      </c>
+      <c r="D1953" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 입출고 확인 단계의 하단 여백 조정</t>
+        </is>
+      </c>
+      <c r="E1953" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1953" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1954" s="15" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1954" s="15" t="inlineStr">
+        <is>
+          <t>0025f804</t>
+        </is>
+      </c>
+      <c r="D1954" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 입출고 작성 단계의 가용 높이 확보</t>
+        </is>
+      </c>
+      <c r="E1954" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1954" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1955" s="7" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1955" s="7" t="inlineStr">
+        <is>
+          <t>93eeba8c</t>
+        </is>
+      </c>
+      <c r="D1955" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 작성 이탈 확인 안내 문구와 정렬 정리</t>
+        </is>
+      </c>
+      <c r="E1955" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1955" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1956" s="15" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1956" s="15" t="inlineStr">
+        <is>
+          <t>265e9706</t>
+        </is>
+      </c>
+      <c r="D1956" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 일보 편집 영역을 화면 높이에 맞게 확장</t>
+        </is>
+      </c>
+      <c r="E1956" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1956" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1957" s="7" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C1957" s="7" t="inlineStr">
+        <is>
+          <t>c2434ab0</t>
+        </is>
+      </c>
+      <c r="D1957" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 daily: 모바일 일보 작성자 목록을 네 열로 배치</t>
+        </is>
+      </c>
+      <c r="E1957" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1957" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1958" s="15" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1958" s="15" t="inlineStr">
+        <is>
+          <t>70819432</t>
+        </is>
+      </c>
+      <c r="D1958" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 daily: 모바일 일보 결과와 빈 화면 높이 확장</t>
+        </is>
+      </c>
+      <c r="E1958" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1958" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1959" s="7" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1959" s="7" t="inlineStr">
+        <is>
+          <t>44cd7926</t>
+        </is>
+      </c>
+      <c r="D1959" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 history: 재고 변동 상세의 단위와 조회 불가 사유 지원</t>
+        </is>
+      </c>
+      <c r="E1959" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1959" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1960" s="15" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1960" s="15" t="inlineStr">
+        <is>
+          <t>eb4b14bc</t>
+        </is>
+      </c>
+      <c r="D1960" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 history: 그룹 대표 내역과 상태 요약 표시 통일</t>
+        </is>
+      </c>
+      <c r="E1960" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1960" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1961" s="7" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1961" s="7" t="inlineStr">
+        <is>
+          <t>99ed15e3</t>
+        </is>
+      </c>
+      <c r="D1961" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 history: 모바일 내역의 처리 정보와 재고 변동 상세 추가</t>
+        </is>
+      </c>
+      <c r="E1961" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1961" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1962" s="15" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1962" s="15" t="inlineStr">
+        <is>
+          <t>e984e3df</t>
+        </is>
+      </c>
+      <c r="D1962" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 history: 모바일 묶음 상세의 로그 매칭과 조회 복구 개선</t>
+        </is>
+      </c>
+      <c r="E1962" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1962" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1963" s="7" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1963" s="7" t="inlineStr">
+        <is>
+          <t>6929855e</t>
+        </is>
+      </c>
+      <c r="D1963" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 history: 불량 생애주기 그룹의 취소 선택 내역 보존</t>
+        </is>
+      </c>
+      <c r="E1963" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1963" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1964" s="15" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1964" s="15" t="inlineStr">
+        <is>
+          <t>2de390d4</t>
+        </is>
+      </c>
+      <c r="D1964" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 history: 내역 그룹 조회 훅을 공통 이름으로 교체</t>
+        </is>
+      </c>
+      <c r="E1964" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1964" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1965" s="7" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1965" s="7" t="inlineStr">
+        <is>
+          <t>5d44c932</t>
+        </is>
+      </c>
+      <c r="D1965" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 history: 모바일 내역을 서버 그룹 조회와 공통 캐시로 전환</t>
+        </is>
+      </c>
+      <c r="E1965" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1965" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1966" s="15" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1966" s="15" t="inlineStr">
+        <is>
+          <t>c11a39f0</t>
+        </is>
+      </c>
+      <c r="D1966" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 inventory: 최근 내역의 모바일 재고 변동 상세와 재시도 제공</t>
+        </is>
+      </c>
+      <c r="E1966" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1966" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1967" s="7" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1967" s="7" t="inlineStr">
+        <is>
+          <t>3f7ccaa6</t>
+        </is>
+      </c>
+      <c r="D1967" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 inventory: 모바일 재고 상세에 정보와 내역 탭 추가</t>
+        </is>
+      </c>
+      <c r="E1967" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1967" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1968" s="15" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1968" s="15" t="inlineStr">
+        <is>
+          <t>9d86a436</t>
+        </is>
+      </c>
+      <c r="D1968" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 대시보드 재고 상세에 탭 화면 연결</t>
+        </is>
+      </c>
+      <c r="E1968" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1968" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1969" s="7" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1969" s="7" t="inlineStr">
+        <is>
+          <t>23bcb75a</t>
+        </is>
+      </c>
+      <c r="D1969" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 defect: 모바일 재작업 경로별 결정과 수량 계산 모델 추가</t>
+        </is>
+      </c>
+      <c r="E1969" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1969" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1970" s="15" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1970" s="15" t="inlineStr">
+        <is>
+          <t>d342e3cc</t>
+        </is>
+      </c>
+      <c r="D1970" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 defect: 모바일 재작업 탐색과 처리 결과 확인 화면 추가</t>
+        </is>
+      </c>
+      <c r="E1970" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1970" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1971" s="7" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1971" s="7" t="inlineStr">
+        <is>
+          <t>539ed6c6</t>
+        </is>
+      </c>
+      <c r="D1971" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 defect: 모바일 사유 입력의 선택 문구 간소화</t>
+        </is>
+      </c>
+      <c r="E1971" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1971" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1972" s="15" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1972" s="15" t="inlineStr">
+        <is>
+          <t>c1a62cb7</t>
+        </is>
+      </c>
+      <c r="D1972" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 defect: 모바일 불량 품목 선택을 두 열 목록으로 정리</t>
+        </is>
+      </c>
+      <c r="E1972" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1972" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1973" s="7" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1973" s="7" t="inlineStr">
+        <is>
+          <t>98d27af5</t>
+        </is>
+      </c>
+      <c r="D1973" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 defect: 모바일 부서별 불량 카드와 기록 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1973" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1973" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1974" s="15" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1974" s="15" t="inlineStr">
+        <is>
+          <t>2e832501</t>
+        </is>
+      </c>
+      <c r="D1974" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 defect: 모바일 불량 보관 필터와 목록 표시 정리</t>
+        </is>
+      </c>
+      <c r="E1974" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1974" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1975" s="7" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1975" s="7" t="inlineStr">
+        <is>
+          <t>9b2d5ae8</t>
+        </is>
+      </c>
+      <c r="D1975" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 defect: 모바일 불량 작업과 재고 출처 선택 화면 추가</t>
+        </is>
+      </c>
+      <c r="E1975" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1975" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1976" s="15" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1976" s="15" t="inlineStr">
+        <is>
+          <t>e20055b3</t>
+        </is>
+      </c>
+      <c r="D1976" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 defect: 불량 처리 단계에 모바일 수량과 재작업 화면 연결</t>
+        </is>
+      </c>
+      <c r="E1976" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1976" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1977" s="7" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1977" s="7" t="inlineStr">
+        <is>
+          <t>86a4e09e</t>
+        </is>
+      </c>
+      <c r="D1977" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 defect: 불량 작업 선택과 처리 단계의 뒤로가기 상태 보존</t>
+        </is>
+      </c>
+      <c r="E1977" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1977" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1978" s="15" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1978" s="15" t="inlineStr">
+        <is>
+          <t>70fd9c57</t>
+        </is>
+      </c>
+      <c r="D1978" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 불량 탭 재진입 시 작업 선택 화면으로 복귀</t>
+        </is>
+      </c>
+      <c r="E1978" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1978" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1979" s="7" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1979" s="7" t="inlineStr">
+        <is>
+          <t>30aaaa8f</t>
+        </is>
+      </c>
+      <c r="D1979" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-01 mobile: 일보 화면에서 하단 더보기 탭 이름 표시</t>
+        </is>
+      </c>
+      <c r="E1979" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1979" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1980" s="15" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="C1980" s="15" t="inlineStr">
+        <is>
+          <t>11c01e63</t>
+        </is>
+      </c>
+      <c r="D1980" s="16" t="inlineStr">
+        <is>
+          <t>Merge branch 'codex/mobile-ui'</t>
+        </is>
+      </c>
+      <c r="E1980" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1980" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1981" s="7" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="C1981" s="7" t="inlineStr">
+        <is>
+          <t>82b2926f</t>
+        </is>
+      </c>
+      <c r="D1981" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-06 mobile: 대시보드 가독성 개선 및 BOM 조회 연결</t>
+        </is>
+      </c>
+      <c r="E1981" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1981" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1982" s="15" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="C1982" s="15" t="inlineStr">
+        <is>
+          <t>2c17a36d</t>
+        </is>
+      </c>
+      <c r="D1982" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-06 defect: 격리 묶음 행 전체 클릭으로 기록 펼침</t>
+        </is>
+      </c>
+      <c r="E1982" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1982" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1983" s="7" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="C1983" s="7" t="inlineStr">
+        <is>
+          <t>251e4820</t>
+        </is>
+      </c>
+      <c r="D1983" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-06 frontend: PC·모바일 알림 읽음 동기화 개선</t>
+        </is>
+      </c>
+      <c r="E1983" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1983" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1984" s="15" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="C1984" s="15" t="inlineStr">
+        <is>
+          <t>8e865173</t>
+        </is>
+      </c>
+      <c r="D1984" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-06 defect: 불량 묶음 행 전체 클릭 펼침 적용</t>
+        </is>
+      </c>
+      <c r="E1984" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1984" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1985" s="7" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="C1985" s="7" t="inlineStr">
+        <is>
+          <t>de243fd8</t>
+        </is>
+      </c>
+      <c r="D1985" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-06 mobile: 대시보드와 체크리스트 디자인 및 모바일 정렬 개선</t>
+        </is>
+      </c>
+      <c r="E1985" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1985" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1986" s="15" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C1986" s="15" t="inlineStr">
+        <is>
+          <t>3bbe524c</t>
+        </is>
+      </c>
+      <c r="D1986" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-06 frontend: 불량 품목 선택 버튼 정렬과 외부 스크롤바 적용</t>
+        </is>
+      </c>
+      <c r="E1986" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1986" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1987" s="7" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="C1987" s="7" t="inlineStr">
+        <is>
+          <t>44a64dd4</t>
+        </is>
+      </c>
+      <c r="D1987" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-06 frontend: 불량 처리 카드 폭 및 사유 필수 입력 적용</t>
+        </is>
+      </c>
+      <c r="E1987" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1987" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1988" s="15" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="C1988" s="15" t="inlineStr">
+        <is>
+          <t>80779db7</t>
+        </is>
+      </c>
+      <c r="D1988" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-06 fix: 거래 유형 진단과 최신 화면 CI 테스트 수정</t>
+        </is>
+      </c>
+      <c r="E1988" s="15" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="F1988" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1989" s="7" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="C1989" s="7" t="inlineStr">
+        <is>
+          <t>0bf403fb</t>
+        </is>
+      </c>
+      <c r="D1989" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-06 notifications: 중앙 알림 팝업과 업무 요약 표시 개선</t>
+        </is>
+      </c>
+      <c r="E1989" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1989" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1990" s="15" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="C1990" s="15" t="inlineStr">
+        <is>
+          <t>9940f023</t>
+        </is>
+      </c>
+      <c r="D1990" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-06 defect: 대표 보고용 불량 통계와 상세 분석 개편</t>
+        </is>
+      </c>
+      <c r="E1990" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1990" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1991" s="7" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="C1991" s="7" t="inlineStr">
+        <is>
+          <t>003c6196</t>
+        </is>
+      </c>
+      <c r="D1991" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-06 frontend: 비활동 작업자 확인 팝업과 덱스레이 이미지 추가</t>
+        </is>
+      </c>
+      <c r="E1991" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1991" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1992" s="15" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="C1992" s="15" t="inlineStr">
+        <is>
+          <t>e11a0c87</t>
+        </is>
+      </c>
+      <c r="D1992" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-06 history: 취소 작업명 표시 수정 및 검토 인수인계 추가</t>
+        </is>
+      </c>
+      <c r="E1992" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1992" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1993" s="19" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="C1993" s="19" t="inlineStr">
+        <is>
+          <t>50e79fac</t>
+        </is>
+      </c>
+      <c r="D1993" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-06 items: 여러 글자 모델 연결과 품목 편집 복원 수정</t>
+        </is>
+      </c>
+      <c r="E1993" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1993" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1994" s="19" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="C1994" s="19" t="inlineStr">
+        <is>
+          <t>d8b020ac</t>
+        </is>
+      </c>
+      <c r="D1994" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-06 admin: 모델 삭제 후 직원 담당 연결 갱신</t>
+        </is>
+      </c>
+      <c r="E1994" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F1994" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1995" s="19" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="C1995" s="19" t="inlineStr">
+        <is>
+          <t>0c7cbcd0</t>
+        </is>
+      </c>
+      <c r="D1995" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-06 shipping: 준비 취소 이후 요청 취소 정합성 수정</t>
+        </is>
+      </c>
+      <c r="E1995" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1995" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1996" s="19" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="C1996" s="19" t="inlineStr">
+        <is>
+          <t>4cb3bd13</t>
+        </is>
+      </c>
+      <c r="D1996" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-06 inventory: 초기 재고 거래와 주간 검산 보완</t>
+        </is>
+      </c>
+      <c r="E1996" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1996" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1997" s="19" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="C1997" s="19" t="inlineStr">
+        <is>
+          <t>a9580af0</t>
+        </is>
+      </c>
+      <c r="D1997" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-06 qa: 브라우저 회귀 검증 스킬과 완료 근거 추가</t>
+        </is>
+      </c>
+      <c r="E1997" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F1997" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1998" s="19" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="C1998" s="19" t="inlineStr">
+        <is>
+          <t>259f6b64</t>
+        </is>
+      </c>
+      <c r="D1998" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-07 mobile: 출하 업무 확장과 전체 화면 디자인 통일</t>
+        </is>
+      </c>
+      <c r="E1998" s="19" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F1998" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1999" s="7" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="C1999" s="7" t="inlineStr">
+        <is>
+          <t>06980c41</t>
+        </is>
+      </c>
+      <c r="D1999" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07 frontend: 번들 크기 예산을 2.95 MB로 조정</t>
+        </is>
+      </c>
+      <c r="E1999" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F1999" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2000" s="15" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="C2000" s="15" t="inlineStr">
+        <is>
+          <t>6f2f1715</t>
+        </is>
+      </c>
+      <c r="D2000" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-07 qa: 화면 변경에 맞춰 CI 회귀 테스트 수정</t>
+        </is>
+      </c>
+      <c r="E2000" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2000" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2001" s="7" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="C2001" s="7" t="inlineStr">
+        <is>
+          <t>b75f60c4</t>
+        </is>
+      </c>
+      <c r="D2001" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07 docs: 플랜 기본 추천 모델을 GPT-6.1 Sol로 갱신</t>
+        </is>
+      </c>
+      <c r="E2001" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F2001" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2002" s="15" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="C2002" s="15" t="inlineStr">
+        <is>
+          <t>6230e37c</t>
+        </is>
+      </c>
+      <c r="D2002" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-07 mobile: 공통 헤더와 재진입·복귀 동작 및 스크롤 경계 통일</t>
+        </is>
+      </c>
+      <c r="E2002" s="15" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F2002" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2003" s="7" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="C2003" s="7" t="inlineStr">
+        <is>
+          <t>7ff9f01c</t>
+        </is>
+      </c>
+      <c r="D2003" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07 mobile: 일보 작성 화면을 남은 높이에 맞추고 기록 요약 적용</t>
+        </is>
+      </c>
+      <c r="E2003" s="7" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="F2003" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2004" s="15" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="C2004" s="15" t="inlineStr">
+        <is>
+          <t>d49d03c5</t>
+        </is>
+      </c>
+      <c r="D2004" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-07 weekly: 모바일 수량 표시와 공정 선택 및 스크롤 곡률 정리</t>
+        </is>
+      </c>
+      <c r="E2004" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2004" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2005" s="7" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="C2005" s="7" t="inlineStr">
+        <is>
+          <t>34890d0f</t>
+        </is>
+      </c>
+      <c r="D2005" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07 docs: 모바일 변경 동작과 QA 검증 기록 갱신</t>
+        </is>
+      </c>
+      <c r="E2005" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F2005" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2006" s="15" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="C2006" s="15" t="inlineStr">
+        <is>
+          <t>0bd0654d</t>
+        </is>
+      </c>
+      <c r="D2006" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-07 admin: 직원 등급과 결재 특례 제거 및 정보 보존</t>
+        </is>
+      </c>
+      <c r="E2006" s="15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2006" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2007" s="7" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="C2007" s="7" t="inlineStr">
+        <is>
+          <t>f662af7d</t>
+        </is>
+      </c>
+      <c r="D2007" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07 settings: 화면 설정 원자 저장과 직원별 탭 동기화</t>
+        </is>
+      </c>
+      <c r="E2007" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2007" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2008" s="15" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="C2008" s="15" t="inlineStr">
+        <is>
+          <t>84c0e826</t>
+        </is>
+      </c>
+      <c r="D2008" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-07 defect: 최초 분류 기준 발생 통계와 손상 이력 안내</t>
+        </is>
+      </c>
+      <c r="E2008" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2008" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2009" s="7" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C2009" s="7" t="inlineStr">
+        <is>
+          <t>b5805302</t>
+        </is>
+      </c>
+      <c r="D2009" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07 inventory: 원자재 입고와 삭제 품목 신규 작업 검증</t>
+        </is>
+      </c>
+      <c r="E2009" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2009" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2010" s="15" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C2010" s="15" t="inlineStr">
+        <is>
+          <t>5de9c635</t>
+        </is>
+      </c>
+      <c r="D2010" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-07 items: 직원별 상세 복원과 삭제·조회 오류 구분</t>
+        </is>
+      </c>
+      <c r="E2010" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2010" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2011" s="7" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="C2011" s="7" t="inlineStr">
+        <is>
+          <t>70c4d7fb</t>
+        </is>
+      </c>
+      <c r="D2011" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07 history: 원작업과 취소 건수 및 기간별 집계 정합성</t>
+        </is>
+      </c>
+      <c r="E2011" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2011" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2012" s="15" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="C2012" s="15" t="inlineStr">
+        <is>
+          <t>8fb3118a</t>
+        </is>
+      </c>
+      <c r="D2012" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-07 qa: 기대값 검증 원장과 브라우저 회귀 근거 정리</t>
+        </is>
+      </c>
+      <c r="E2012" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2012" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2013" s="7" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="C2013" s="7" t="inlineStr">
+        <is>
+          <t>37521e12</t>
+        </is>
+      </c>
+      <c r="D2013" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07 defect: 제출별 내역 묶음과 불량 사유 관리 구현</t>
+        </is>
+      </c>
+      <c r="E2013" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2013" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2014" s="15" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C2014" s="15" t="inlineStr">
+        <is>
+          <t>bf40aaf2</t>
+        </is>
+      </c>
+      <c r="D2014" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-07 qa: 생산 BOM 펼침 검증의 클릭 대상 안정화</t>
+        </is>
+      </c>
+      <c r="E2014" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2014" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2015" s="7" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="C2015" s="7" t="inlineStr">
+        <is>
+          <t>03603b63</t>
+        </is>
+      </c>
+      <c r="D2015" s="8" t="inlineStr">
+        <is>
+          <t>Merge commit '8fb3118ac8a7a43e13cd2d2800a160c35493b52e' into HEAD</t>
+        </is>
+      </c>
+      <c r="E2015" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2015" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2016" s="15" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="C2016" s="15" t="inlineStr">
+        <is>
+          <t>53b73567</t>
+        </is>
+      </c>
+      <c r="D2016" s="16" t="inlineStr">
+        <is>
+          <t>Merge branch 'main' into HEAD</t>
+        </is>
+      </c>
+      <c r="E2016" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2016" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2017" s="7" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="C2017" s="7" t="inlineStr">
+        <is>
+          <t>4366449a</t>
+        </is>
+      </c>
+      <c r="D2017" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07 qa: 이력 하위 작업 그룹의 테스트 기대값 동기화</t>
+        </is>
+      </c>
+      <c r="E2017" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2017" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2018" s="15" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="C2018" s="15" t="inlineStr">
+        <is>
+          <t>6abe6d0d</t>
+        </is>
+      </c>
+      <c r="D2018" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-07 qa: 불량 사유 선택과 정리 요청의 브라우저 회귀 보완</t>
+        </is>
+      </c>
+      <c r="E2018" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2018" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2019" s="7" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="C2019" s="7" t="inlineStr">
+        <is>
+          <t>8523f4d0</t>
+        </is>
+      </c>
+      <c r="D2019" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07 frontend: 승인된 번들 예산 조정과 CI 회귀 근거 기록</t>
+        </is>
+      </c>
+      <c r="E2019" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2019" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2020" s="15" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="C2020" s="15" t="inlineStr">
+        <is>
+          <t>74d07292</t>
+        </is>
+      </c>
+      <c r="D2020" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-07 qa: 사유 필수값을 재고 운영 회귀 테스트에 반영</t>
+        </is>
+      </c>
+      <c r="E2020" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2020" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2021" s="7" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="C2021" s="7" t="inlineStr">
+        <is>
+          <t>2a27a6e1</t>
+        </is>
+      </c>
+      <c r="D2021" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07 qa: PostgreSQL 사유 타입과 백업 출처 검증 계약 보완</t>
+        </is>
+      </c>
+      <c r="E2021" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2021" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2022" s="15" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="C2022" s="15" t="inlineStr">
+        <is>
+          <t>d9c1df01</t>
+        </is>
+      </c>
+      <c r="D2022" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-07 ops: SQLite 사전검증의 PostgreSQL 전용 변경 판별 보완</t>
+        </is>
+      </c>
+      <c r="E2022" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2022" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2023" s="7" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="C2023" s="7" t="inlineStr">
+        <is>
+          <t>a8eda817</t>
+        </is>
+      </c>
+      <c r="D2023" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07 defect: 사유 선택창 반응형 배치와 개발 복구 기록 정리</t>
+        </is>
+      </c>
+      <c r="E2023" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2023" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B2024" s="15" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C2024" s="15" t="inlineStr">
+        <is>
+          <t>353ee530</t>
+        </is>
+      </c>
+      <c r="D2024" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-08 io: 튜브 원자재 입출고 및 전용 업체 관리 추가</t>
+        </is>
+      </c>
+      <c r="E2024" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2024" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B2025" s="7" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="C2025" s="7" t="inlineStr">
+        <is>
+          <t>80f10b73</t>
+        </is>
+      </c>
+      <c r="D2025" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-08 test: 마이그레이션 최신 버전 기대값 갱신</t>
+        </is>
+      </c>
+      <c r="E2025" s="7" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F2025" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B2026" s="15" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="C2026" s="15" t="inlineStr">
+        <is>
+          <t>2d79cd28</t>
+        </is>
+      </c>
+      <c r="D2026" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-08 ops: 배포 정지 중 감시 프로세스 재기동 방지</t>
+        </is>
+      </c>
+      <c r="E2026" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2026" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E135"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="67.25" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2025건 (회사 기간 670건)</t>
+          <t>2182건 (회사 기간 670건)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>477건 (평일 야간·주말·휴가 시간 커밋)</t>
+          <t>538건 (평일 야간·주말·휴가 시간 커밋)</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>109 / 118개 (92%)</t>
+          <t>112 / 121개 (93%)</t>
         </is>
       </c>
     </row>
@@ -4318,10 +4318,295 @@
         </is>
       </c>
     </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-10-12  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (5)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-10-13  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (4)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-10-14  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (32)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-10-15  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (20)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-10-16  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (5)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-10-19  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■■■■■■■■■■■■■■■■■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (60)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-10-20  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (11)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-10-21  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■■■■■■■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (14)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-10-22  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00ED7D31"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (5)</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">2026-10-23  </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>■</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="00000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  (1)</t>
+          </r>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="133">
+  <mergeCells count="143">
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A142:E142"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A45:E45"/>
@@ -4331,14 +4616,17 @@
     <mergeCell ref="A87:E87"/>
     <mergeCell ref="A65:E65"/>
     <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A137:E137"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A136:E136"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A105:E105"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A139:E139"/>
     <mergeCell ref="A71:E71"/>
     <mergeCell ref="A129:E129"/>
     <mergeCell ref="A23:E23"/>
@@ -4355,6 +4643,7 @@
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A83:E83"/>
     <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A138:E138"/>
     <mergeCell ref="A132:E132"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="A119:E119"/>
@@ -4401,8 +4690,10 @@
     <mergeCell ref="A86:E86"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A141:E141"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A135:E135"/>
+    <mergeCell ref="A144:E144"/>
     <mergeCell ref="A122:E122"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A125:E125"/>
@@ -4434,6 +4725,7 @@
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A145:E145"/>
     <mergeCell ref="A101:E101"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
@@ -4441,6 +4733,7 @@
     <mergeCell ref="A116:E116"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A126:E126"/>
+    <mergeCell ref="A140:E140"/>
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A35:E35"/>
@@ -4452,6 +4745,7 @@
     <mergeCell ref="A102:E102"/>
     <mergeCell ref="A117:E117"/>
     <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A143:E143"/>
     <mergeCell ref="A92:E92"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4464,7 +4758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5063,6 +5357,57 @@
         <v>181</v>
       </c>
     </row>
+    <row r="25" ht="97.19999999999999" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-09 ~ 10-16</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>전수조사·불량·결재 개선</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>재고 전수조사 회차·계수·검토·종료·내보내기 화면 정비
+품목 별칭·공통 동의어를 컴퓨터·모바일 검색에 적용
+불량 격리·처리 단계와 창고 정상 복귀 개선
+AS·연구용 사용출고 차감·반환 안내 보강
+창고·생산부 결재 역할 분리 및 혼합 공정 요청 연결
+품목 최근 이력·작업 결과와 모바일 재고·알림 화면 개선</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" ht="113.4" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-19 ~ 10-23</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>불량·관리·작업 예약 개선</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>불량 발생 통계와 처리 단계·수량 확인 개선
+관리자 품목·모델·직원·부서 목록 및 정보 입력 화면 정비
+권한 변경 시 작성 내용과 진행 중인 결재 보존
+품목 검색과 입출고 내역 확인 편의 개선
+컴퓨터·모바일 입출고 방향 안내와 취소 처리 개선
+작업 예약·공유 작업 현황 및 상세 확인 추가
+전수조사 대기 화면과 로그인 로고 표시 개선</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5074,7 +5419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7753,77 +8098,77 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="12" t="n">
+      <c r="A111" s="9" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="13" t="inlineStr">
-        <is>
-          <t>실 재고 데이터 입력 + 직원 테스트</t>
-        </is>
-      </c>
-      <c r="C111" s="12" t="inlineStr">
-        <is>
-          <t>데이터</t>
-        </is>
-      </c>
-      <c r="D111" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E111" s="13" t="inlineStr">
-        <is>
-          <t>BOM·입출고 정리 후</t>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>재고 전수조사 회차 관리</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E111" s="10" t="inlineStr">
+        <is>
+          <t>회차 시작·계수·검토·종료·결과 내보내기</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="12" t="n">
+      <c r="A112" s="9" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="13" t="inlineStr">
-        <is>
-          <t>불량 처리 흐름 Phase 2</t>
-        </is>
-      </c>
-      <c r="C112" s="12" t="inlineStr">
-        <is>
-          <t>생산</t>
-        </is>
-      </c>
-      <c r="D112" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E112" s="13" t="inlineStr">
-        <is>
-          <t>부서 결재·집계·자동화</t>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>품목 별칭·공통 동의어 검색</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E112" s="10" t="inlineStr">
+        <is>
+          <t>공용 검색어 등록과 컴퓨터·모바일 통합 검색</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="12" t="n">
+      <c r="A113" s="9" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="13" t="inlineStr">
-        <is>
-          <t>역할별 접근 권한 연동</t>
-        </is>
-      </c>
-      <c r="C113" s="12" t="inlineStr">
-        <is>
-          <t>보안</t>
-        </is>
-      </c>
-      <c r="D113" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E113" s="13" t="inlineStr">
-        <is>
-          <t>부서·역할 기반 (PIN 로그인 완료)</t>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>공유 작업 예약·현황 확인</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr">
+        <is>
+          <t>작업 예약과 공유 작업 상태·상세 확인</t>
         </is>
       </c>
     </row>
@@ -7833,12 +8178,12 @@
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>총재고 / 가용재고 / 예약재고 분리</t>
+          <t>실 재고 데이터 입력 + 직원 테스트</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>재고</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
@@ -7848,7 +8193,7 @@
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>재고 가용성 계산 고도화</t>
+          <t>BOM·입출고 정리 후</t>
         </is>
       </c>
     </row>
@@ -7858,12 +8203,12 @@
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>외부 접근 환경 구성</t>
+          <t>불량 처리 흐름 Phase 2</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D115" s="14" t="inlineStr">
@@ -7873,7 +8218,7 @@
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>PC 또는 NAS 서버 + API 인증</t>
+          <t>부서 결재·집계·자동화</t>
         </is>
       </c>
     </row>
@@ -7883,12 +8228,12 @@
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>발주 관리</t>
+          <t>역할별 접근 권한 연동</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr">
@@ -7896,7 +8241,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E116" s="13" t="inlineStr"/>
+      <c r="E116" s="13" t="inlineStr">
+        <is>
+          <t>부서·역할 기반 (PIN 로그인 완료)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="12" t="n">
@@ -7904,12 +8253,12 @@
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>생산 실적 / 원가 관리</t>
+          <t>총재고 / 가용재고 / 예약재고 분리</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>재고</t>
         </is>
       </c>
       <c r="D117" s="14" t="inlineStr">
@@ -7917,7 +8266,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E117" s="13" t="inlineStr"/>
+      <c r="E117" s="13" t="inlineStr">
+        <is>
+          <t>재고 가용성 계산 고도화</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="12" t="n">
@@ -7925,12 +8278,12 @@
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>부서별 생산진행도 대시보드</t>
+          <t>외부 접근 환경 구성</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>인프라</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
@@ -7940,7 +8293,7 @@
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>사장님 요청 — 검토 중</t>
+          <t>PC 또는 NAS 서버 + API 인증</t>
         </is>
       </c>
     </row>
@@ -7950,20 +8303,87 @@
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
+          <t>발주 관리</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>구매</t>
+        </is>
+      </c>
+      <c r="D119" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E119" s="13" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="12" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="13" t="inlineStr">
+        <is>
+          <t>생산 실적 / 원가 관리</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>생산</t>
+        </is>
+      </c>
+      <c r="D120" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E120" s="13" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="13" t="inlineStr">
+        <is>
+          <t>부서별 생산진행도 대시보드</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D121" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E121" s="13" t="inlineStr">
+        <is>
+          <t>사장님 요청 — 검토 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="12" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="13" t="inlineStr">
+        <is>
           <t>출하 거래처 관리</t>
         </is>
       </c>
-      <c r="C119" s="12" t="inlineStr">
+      <c r="C122" s="12" t="inlineStr">
         <is>
           <t>출하</t>
         </is>
       </c>
-      <c r="D119" s="14" t="inlineStr">
+      <c r="D122" s="14" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E119" s="13" t="inlineStr">
+      <c r="E122" s="13" t="inlineStr">
         <is>
           <t>거래처 마스터 + 출하 이력</t>
         </is>
@@ -7980,7 +8400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D126"/>
+  <dimension ref="A1:D136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10969,6 +11389,241 @@
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="67.5" customHeight="1">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12 frontend: 품목 최근 내역 전체 조회와 더 보기 추가
+2026-10-12 frontend: 모바일 생산 요약 클릭과 상세창 여백 통일
+2026-10-12 backend: 명세 생성 일치를 위해 Pydantic 버전 고정
+2026-10-12 defect: 동일 품목 사유별 일괄 격리와 모바일 입력 개선
+2026-10-12 weekly: 9월 24일~10월 8일 주간보고 갱신</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="54" customHeight="1">
+      <c r="A128" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B128" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C128" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-13 frontend: 모바일 알림창 통일과 로그인 팝업 설정 적용
+2026-10-13 ops: 배포 캐시 자동 정리와 설치본 보존 적용
+2026-10-13 defect: 정상 복귀 사유 제거와 메모 이동 모션 적용
+2026-10-13 history: 취소 차단 사유와 비활성 버튼 표시 수정</t>
+        </is>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="67.5" customHeight="1">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 history: 불용 표시와 내 내역 필터 적용
+2026-10-14 backend: 전수조사 모델과 병합 마이그레이션 추가
+2026-10-14 backend: 작업자 로그인 세션과 직원 PIN 계약 연결
+2026-10-14 backend: 공동재고 범위와 POOL 전환 기반 추가
+2026-10-14 backend: 기존 재고와 불량 소비자의 POOL 연동</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="67.5" customHeight="1">
+      <c r="A130" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B130" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="C130" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 frontend: 비동기 로그아웃 테스트의 완료 대기 수정
+2026-10-15 defect: 부서 필터 회귀 검사를 현재 부서 칩에 맞춤
+2026-10-15 defect: 좁은 PC 사유 입력 E2E의 컨테이너 배치 검증 보완
+2026-10-15 defect: 격리 원장 E2E에 선택 사유 정상 복귀 계약 반영
+2026-10-15 defect: 격리 복귀 E2E의 생성 기록 격리와 요청 증빙 검증</t>
+        </is>
+      </c>
+      <c r="D130" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="67.5" customHeight="1">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16 approval: 창고와 생산부 결재 권한 분리
+2026-10-16 io: 창고 직원의 혼합 공정 요청을 생산부 결재로 연결
+2026-10-16 frontend: PC와 모바일 자동 승인 안내를 독립 결재 역할에 맞춤
+2026-10-16 docs: 생산부 전체 공정 결재 정책과 권한 검증 근거 기록
+2026-10-16 inventory: 창고 격리 재고의 정상 복귀 위치 수정</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="67.5" customHeight="1">
+      <c r="A132" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B132" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="C132" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-19 history: 초기 재고 등록 작업명·경로와 자동 메모 표시 수정
+2026-10-19 frontend: 대시보드 품목명 복사 버튼 추가
+2026-10-19 search: 쉼표 OR 품목 검색 지원
+2026-10-19 defect: 직접 처리 로그의 창고 출처 판별 보완
+2026-10-19 defect: 최초 분류 필터와 분류별 전체 수량 제공</t>
+        </is>
+      </c>
+      <c r="D132" s="15" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="67.5" customHeight="1">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20 backend: 실사 잘못된 커서 테스트에 검색 설정 버전 반영
+2026-10-20 defect: 불량 목록 정렬 칩 테스트 기대값 갱신
+2026-10-20 frontend: 전체화면 테스트의 권한 회수 훅 모의 보완
+2026-10-20 history: 조합 중 즉시 검색 테스트 계약 갱신
+2026-10-20 defect: E2E 불량 단계 이동과 필터 동선 갱신</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="67.5" customHeight="1">
+      <c r="A134" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B134" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C134" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-21 workflow: 논리적 단위별 커밋과 이력 재구성 규칙 명시
+2026-10-21 admin: 공통 전환 효과와 목록 렌더링 기반 개선
+2026-10-21 admin: 조회 캐시와 저장 중복 및 늦은 응답 보호
+2026-10-21 admin: 모델 직원 부서 선택과 미저장 입력 보호
+2026-10-21 items: 상세 입력 보호와 목록 상태 복원</t>
+        </is>
+      </c>
+      <c r="D134" s="15" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="67.5" customHeight="1">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-22 backend: 승인된 입출고 작업의 요청자 취소 권한 수정
+2026-10-22 frontend: BOM 잠금 안내와 검색창 스켈레톤 배치 정렬
+2026-10-22 frontend: 대시보드 검색창과 스크롤 스켈레톤 정합성 개선
+2026-10-22 mes: 작업 예약과 공유 작업 현황 및 상세 화면 통합
+2026-10-22 docs: 메인 예약 전환과 재기동 검증 기록</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="27" customHeight="1">
+      <c r="A136" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B136" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23 frontend: 대시보드 스켈레톤 스크롤 높이를 실제 목록과 동기화</t>
+        </is>
+      </c>
+      <c r="D136" s="15" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
@@ -10985,7 +11640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2026"/>
+  <dimension ref="A1:F2183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -75828,6 +76483,5030 @@
         </is>
       </c>
     </row>
+    <row r="2027">
+      <c r="A2027" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2027" s="7" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="C2027" s="7" t="inlineStr">
+        <is>
+          <t>07f91cb5</t>
+        </is>
+      </c>
+      <c r="D2027" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12 frontend: 품목 최근 내역 전체 조회와 더 보기 추가</t>
+        </is>
+      </c>
+      <c r="E2027" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2027" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2028" s="15" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="C2028" s="15" t="inlineStr">
+        <is>
+          <t>5a2399a4</t>
+        </is>
+      </c>
+      <c r="D2028" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-12 frontend: 모바일 생산 요약 클릭과 상세창 여백 통일</t>
+        </is>
+      </c>
+      <c r="E2028" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2028" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2029" s="7" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="C2029" s="7" t="inlineStr">
+        <is>
+          <t>63f2ac4c</t>
+        </is>
+      </c>
+      <c r="D2029" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12 backend: 명세 생성 일치를 위해 Pydantic 버전 고정</t>
+        </is>
+      </c>
+      <c r="E2029" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2029" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2030" s="15" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="C2030" s="15" t="inlineStr">
+        <is>
+          <t>d9f5be45</t>
+        </is>
+      </c>
+      <c r="D2030" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-12 defect: 동일 품목 사유별 일괄 격리와 모바일 입력 개선</t>
+        </is>
+      </c>
+      <c r="E2030" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2030" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2031" s="7" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="C2031" s="7" t="inlineStr">
+        <is>
+          <t>1eae6d0c</t>
+        </is>
+      </c>
+      <c r="D2031" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-12 weekly: 9월 24일~10월 8일 주간보고 갱신</t>
+        </is>
+      </c>
+      <c r="E2031" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2031" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2032" s="15" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C2032" s="15" t="inlineStr">
+        <is>
+          <t>c77e484c</t>
+        </is>
+      </c>
+      <c r="D2032" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-13 frontend: 모바일 알림창 통일과 로그인 팝업 설정 적용</t>
+        </is>
+      </c>
+      <c r="E2032" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2032" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2033" s="7" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="C2033" s="7" t="inlineStr">
+        <is>
+          <t>849aa7ad</t>
+        </is>
+      </c>
+      <c r="D2033" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-13 ops: 배포 캐시 자동 정리와 설치본 보존 적용</t>
+        </is>
+      </c>
+      <c r="E2033" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2033" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2034" s="15" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="C2034" s="15" t="inlineStr">
+        <is>
+          <t>be5cbeab</t>
+        </is>
+      </c>
+      <c r="D2034" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-13 defect: 정상 복귀 사유 제거와 메모 이동 모션 적용</t>
+        </is>
+      </c>
+      <c r="E2034" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2034" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2035" s="7" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="C2035" s="7" t="inlineStr">
+        <is>
+          <t>be658b4f</t>
+        </is>
+      </c>
+      <c r="D2035" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-13 history: 취소 차단 사유와 비활성 버튼 표시 수정</t>
+        </is>
+      </c>
+      <c r="E2035" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2035" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2036" s="15" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="C2036" s="15" t="inlineStr">
+        <is>
+          <t>837b0bb3</t>
+        </is>
+      </c>
+      <c r="D2036" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 history: 불용 표시와 내 내역 필터 적용</t>
+        </is>
+      </c>
+      <c r="E2036" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2036" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2037" s="7" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="C2037" s="7" t="inlineStr">
+        <is>
+          <t>85715291</t>
+        </is>
+      </c>
+      <c r="D2037" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 backend: 전수조사 모델과 병합 마이그레이션 추가</t>
+        </is>
+      </c>
+      <c r="E2037" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2037" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2038" s="15" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="C2038" s="15" t="inlineStr">
+        <is>
+          <t>c3a15f04</t>
+        </is>
+      </c>
+      <c r="D2038" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 backend: 작업자 로그인 세션과 직원 PIN 계약 연결</t>
+        </is>
+      </c>
+      <c r="E2038" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2038" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2039" s="7" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="C2039" s="7" t="inlineStr">
+        <is>
+          <t>7aa6ff95</t>
+        </is>
+      </c>
+      <c r="D2039" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 backend: 공동재고 범위와 POOL 전환 기반 추가</t>
+        </is>
+      </c>
+      <c r="E2039" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2039" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2040" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2040" s="15" t="inlineStr">
+        <is>
+          <t>7f08d2a9</t>
+        </is>
+      </c>
+      <c r="D2040" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 backend: 기존 재고와 불량 소비자의 POOL 연동</t>
+        </is>
+      </c>
+      <c r="E2040" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2040" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2041" s="7" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2041" s="7" t="inlineStr">
+        <is>
+          <t>741245cf</t>
+        </is>
+      </c>
+      <c r="D2041" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 backend: 예약 출하 취소의 조사 충돌 보호</t>
+        </is>
+      </c>
+      <c r="E2041" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2041" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2042" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2042" s="15" t="inlineStr">
+        <is>
+          <t>b4a9778f</t>
+        </is>
+      </c>
+      <c r="D2042" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 backend: 전수조사 대상과 회차 생명주기 추가</t>
+        </is>
+      </c>
+      <c r="E2042" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2042" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2043" s="7" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2043" s="7" t="inlineStr">
+        <is>
+          <t>08b99c28</t>
+        </is>
+      </c>
+      <c r="D2043" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 backend: 계수 초안 확인과 동시성 보호</t>
+        </is>
+      </c>
+      <c r="E2043" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2043" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2044" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2044" s="15" t="inlineStr">
+        <is>
+          <t>eae40a20</t>
+        </is>
+      </c>
+      <c r="D2044" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 backend: 위치별 반영과 실사 관측 추가</t>
+        </is>
+      </c>
+      <c r="E2044" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2044" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2045" s="7" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2045" s="7" t="inlineStr">
+        <is>
+          <t>8d8ca57a</t>
+        </is>
+      </c>
+      <c r="D2045" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 backend: 일괄 반영과 요청 영수증 복구 추가</t>
+        </is>
+      </c>
+      <c r="E2045" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2045" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2046" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2046" s="15" t="inlineStr">
+        <is>
+          <t>c33e525c</t>
+        </is>
+      </c>
+      <c r="D2046" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 backend: 전체 부분 종료와 증빙 검증 추가</t>
+        </is>
+      </c>
+      <c r="E2046" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2046" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2047" s="7" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2047" s="7" t="inlineStr">
+        <is>
+          <t>b33c9970</t>
+        </is>
+      </c>
+      <c r="D2047" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 backend: 업무 정정과 부서 결재 권한 추가</t>
+        </is>
+      </c>
+      <c r="E2047" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2047" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2048" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2048" s="15" t="inlineStr">
+        <is>
+          <t>66483916</t>
+        </is>
+      </c>
+      <c r="D2048" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 backend: 전수조사 진행과 작업자 집계 추가</t>
+        </is>
+      </c>
+      <c r="E2048" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2048" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2049" s="7" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2049" s="7" t="inlineStr">
+        <is>
+          <t>f57ca3af</t>
+        </is>
+      </c>
+      <c r="D2049" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 history: 작업 이력 투영과 읽기 API 통합</t>
+        </is>
+      </c>
+      <c r="E2049" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2049" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2050" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2050" s="15" t="inlineStr">
+        <is>
+          <t>5c2675fa</t>
+        </is>
+      </c>
+      <c r="D2050" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 backend: 전수조사 라우터와 서버 업무 연결</t>
+        </is>
+      </c>
+      <c r="E2050" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2050" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2051" s="7" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2051" s="7" t="inlineStr">
+        <is>
+          <t>7874353e</t>
+        </is>
+      </c>
+      <c r="D2051" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 frontend: 로그인 세션과 계정 전환 복구 연결</t>
+        </is>
+      </c>
+      <c r="E2051" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2051" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2052" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2052" s="15" t="inlineStr">
+        <is>
+          <t>40a96f5e</t>
+        </is>
+      </c>
+      <c r="D2052" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 frontend: 전수조사 API와 명령 저널 추가</t>
+        </is>
+      </c>
+      <c r="E2052" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2052" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2053" s="7" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2053" s="7" t="inlineStr">
+        <is>
+          <t>dc34f79e</t>
+        </is>
+      </c>
+      <c r="D2053" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 frontend: 메뉴 권한과 참여자 일괄 표시 연결</t>
+        </is>
+      </c>
+      <c r="E2053" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2053" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2054" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2054" s="15" t="inlineStr">
+        <is>
+          <t>f9dfe0fa</t>
+        </is>
+      </c>
+      <c r="D2054" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 stocktake: 계수 편집과 조사 대상 목록 추가</t>
+        </is>
+      </c>
+      <c r="E2054" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2054" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2055" s="7" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2055" s="7" t="inlineStr">
+        <is>
+          <t>e819cef8</t>
+        </is>
+      </c>
+      <c r="D2055" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 stocktake: 반영 대기와 명령 복구 화면 연결</t>
+        </is>
+      </c>
+      <c r="E2055" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2055" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2056" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2056" s="15" t="inlineStr">
+        <is>
+          <t>abba525e</t>
+        </is>
+      </c>
+      <c r="D2056" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 stocktake: 진행 그래프와 로딩 화면 추가</t>
+        </is>
+      </c>
+      <c r="E2056" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2056" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2057" s="7" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2057" s="7" t="inlineStr">
+        <is>
+          <t>79e04a3a</t>
+        </is>
+      </c>
+      <c r="D2057" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 stocktake: 회차 관리와 종료 검토 화면 추가</t>
+        </is>
+      </c>
+      <c r="E2057" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2057" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2058" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2058" s="15" t="inlineStr">
+        <is>
+          <t>1e1249b5</t>
+        </is>
+      </c>
+      <c r="D2058" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 stocktake: 업무 정정 검토 화면 추가</t>
+        </is>
+      </c>
+      <c r="E2058" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2058" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2059" s="7" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2059" s="7" t="inlineStr">
+        <is>
+          <t>c5f5bde8</t>
+        </is>
+      </c>
+      <c r="D2059" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 frontend: PC 모바일 화면 전환과 입력 보호 연결</t>
+        </is>
+      </c>
+      <c r="E2059" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2059" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2060" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2060" s="15" t="inlineStr">
+        <is>
+          <t>3c900080</t>
+        </is>
+      </c>
+      <c r="D2060" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 admin: 직원 상세 배치와 메뉴 카드 개선</t>
+        </is>
+      </c>
+      <c r="E2060" s="15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2060" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2061" s="7" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2061" s="7" t="inlineStr">
+        <is>
+          <t>0b475b48</t>
+        </is>
+      </c>
+      <c r="D2061" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 inventory: 공통 재고표와 모바일 검색 도구줄 적용</t>
+        </is>
+      </c>
+      <c r="E2061" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2061" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2062" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2062" s="15" t="inlineStr">
+        <is>
+          <t>82a91bc8</t>
+        </is>
+      </c>
+      <c r="D2062" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 history: 품목 최근 이력과 작업 상세 통합</t>
+        </is>
+      </c>
+      <c r="E2062" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2062" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2063" s="7" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2063" s="7" t="inlineStr">
+        <is>
+          <t>b2e9b89c</t>
+        </is>
+      </c>
+      <c r="D2063" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 history: 실사 증빙과 달력 표시 회귀 보존</t>
+        </is>
+      </c>
+      <c r="E2063" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2063" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2064" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2064" s="15" t="inlineStr">
+        <is>
+          <t>2b37b711</t>
+        </is>
+      </c>
+      <c r="D2064" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 defect: 공동재고 불량 화면과 색상 토큰 연결</t>
+        </is>
+      </c>
+      <c r="E2064" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2064" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2065" s="7" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2065" s="7" t="inlineStr">
+        <is>
+          <t>44038533</t>
+        </is>
+      </c>
+      <c r="D2065" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-14 frontend: 전수조사 내보내기와 빌드 검증 연결</t>
+        </is>
+      </c>
+      <c r="E2065" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2065" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2066" s="15" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2066" s="15" t="inlineStr">
+        <is>
+          <t>63d1d731</t>
+        </is>
+      </c>
+      <c r="D2066" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-14 docs: 전수조사 통합 검증과 원본 보존 기록</t>
+        </is>
+      </c>
+      <c r="E2066" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F2066" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2067" s="19" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="C2067" s="19" t="inlineStr">
+        <is>
+          <t>9e5a680f</t>
+        </is>
+      </c>
+      <c r="D2067" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-14 frontend: 작업 상세 한글화와 품목 역할 구분</t>
+        </is>
+      </c>
+      <c r="E2067" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2067" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2068" s="15" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="C2068" s="15" t="inlineStr">
+        <is>
+          <t>745b42cc</t>
+        </is>
+      </c>
+      <c r="D2068" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 frontend: 비동기 로그아웃 테스트의 완료 대기 수정</t>
+        </is>
+      </c>
+      <c r="E2068" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2068" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2069" s="7" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="C2069" s="7" t="inlineStr">
+        <is>
+          <t>ff5088da</t>
+        </is>
+      </c>
+      <c r="D2069" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15 defect: 부서 필터 회귀 검사를 현재 부서 칩에 맞춤</t>
+        </is>
+      </c>
+      <c r="E2069" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2069" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2070" s="15" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="C2070" s="15" t="inlineStr">
+        <is>
+          <t>9a06ae0b</t>
+        </is>
+      </c>
+      <c r="D2070" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 defect: 좁은 PC 사유 입력 E2E의 컨테이너 배치 검증 보완</t>
+        </is>
+      </c>
+      <c r="E2070" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2070" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2071" s="7" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="C2071" s="7" t="inlineStr">
+        <is>
+          <t>d2e50b4b</t>
+        </is>
+      </c>
+      <c r="D2071" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15 defect: 격리 원장 E2E에 선택 사유 정상 복귀 계약 반영</t>
+        </is>
+      </c>
+      <c r="E2071" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2071" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2072" s="15" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="C2072" s="15" t="inlineStr">
+        <is>
+          <t>f6e31cde</t>
+        </is>
+      </c>
+      <c r="D2072" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 defect: 격리 복귀 E2E의 생성 기록 격리와 요청 증빙 검증</t>
+        </is>
+      </c>
+      <c r="E2072" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2072" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2073" s="7" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="C2073" s="7" t="inlineStr">
+        <is>
+          <t>9c7f150a</t>
+        </is>
+      </c>
+      <c r="D2073" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15 docs: 전수조사 CI 원인과 회귀 검증 결과 기록</t>
+        </is>
+      </c>
+      <c r="E2073" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F2073" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2074" s="15" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="C2074" s="15" t="inlineStr">
+        <is>
+          <t>1fbfca85</t>
+        </is>
+      </c>
+      <c r="D2074" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 ops: 재고 실사 병합 마이그레이션 자동 배포 정책 추가</t>
+        </is>
+      </c>
+      <c r="E2074" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2074" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2075" s="7" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="C2075" s="7" t="inlineStr">
+        <is>
+          <t>723d18bc</t>
+        </is>
+      </c>
+      <c r="D2075" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15 backend: 전수조사 최근 종료 결과 요약 조회 추가</t>
+        </is>
+      </c>
+      <c r="E2075" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2075" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2076" s="15" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="C2076" s="15" t="inlineStr">
+        <is>
+          <t>61a4aceb</t>
+        </is>
+      </c>
+      <c r="D2076" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 stocktake: 새 회차 시작 폼 초점과 완료 복귀 연결</t>
+        </is>
+      </c>
+      <c r="E2076" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2076" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2077" s="7" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C2077" s="7" t="inlineStr">
+        <is>
+          <t>6dc149db</t>
+        </is>
+      </c>
+      <c r="D2077" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15 stocktake: 회차 없는 대기 화면과 최근 결과 표시</t>
+        </is>
+      </c>
+      <c r="E2077" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2077" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2078" s="15" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C2078" s="15" t="inlineStr">
+        <is>
+          <t>029275b6</t>
+        </is>
+      </c>
+      <c r="D2078" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 frontend: 전수조사 대기 화면에 덱스레이와 반응형 배치 적용</t>
+        </is>
+      </c>
+      <c r="E2078" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2078" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2079" s="7" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C2079" s="7" t="inlineStr">
+        <is>
+          <t>2aa36e85</t>
+        </is>
+      </c>
+      <c r="D2079" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15 docs: 전수조사 대기 화면 구현과 검증 기록 정리</t>
+        </is>
+      </c>
+      <c r="E2079" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F2079" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2080" s="15" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="C2080" s="15" t="inlineStr">
+        <is>
+          <t>ec745320</t>
+        </is>
+      </c>
+      <c r="D2080" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 frontend: 작업 상세 결과 중심 정리와 최근 내역 표시 수정</t>
+        </is>
+      </c>
+      <c r="E2080" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2080" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2081" s="7" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="C2081" s="7" t="inlineStr">
+        <is>
+          <t>2ade4e71</t>
+        </is>
+      </c>
+      <c r="D2081" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15 defect: 불량 화면 통일과 처리 단계 분리</t>
+        </is>
+      </c>
+      <c r="E2081" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2081" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2082" s="15" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="C2082" s="15" t="inlineStr">
+        <is>
+          <t>ad15baf5</t>
+        </is>
+      </c>
+      <c r="D2082" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 search: 품목 별칭과 동의어 검색을 공통화</t>
+        </is>
+      </c>
+      <c r="E2082" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2082" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2083" s="7" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="C2083" s="7" t="inlineStr">
+        <is>
+          <t>211ebbfe</t>
+        </is>
+      </c>
+      <c r="D2083" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15 docs: 검색 기능 통합과 워크트리 정리 기록</t>
+        </is>
+      </c>
+      <c r="E2083" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F2083" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2084" s="15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C2084" s="15" t="inlineStr">
+        <is>
+          <t>89ca19c9</t>
+        </is>
+      </c>
+      <c r="D2084" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 defect: 품목 목록 전체 화면과 입력 조작 영역 개선</t>
+        </is>
+      </c>
+      <c r="E2084" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2084" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2085" s="7" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="C2085" s="7" t="inlineStr">
+        <is>
+          <t>2849ac49</t>
+        </is>
+      </c>
+      <c r="D2085" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15 fix: SQLite 잠금 완화와 불량 처리 입력 개선</t>
+        </is>
+      </c>
+      <c r="E2085" s="7" t="inlineStr">
+        <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="F2085" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2086" s="15" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="C2086" s="15" t="inlineStr">
+        <is>
+          <t>0f3dd2dc</t>
+        </is>
+      </c>
+      <c r="D2086" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-15 io: 사용출고 상위 차감·하위 반환과 방식 안내 팝업 추가</t>
+        </is>
+      </c>
+      <c r="E2086" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2086" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2087" s="7" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="C2087" s="7" t="inlineStr">
+        <is>
+          <t>15e596f4</t>
+        </is>
+      </c>
+      <c r="D2087" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-15 defect: 단계 색상과 품목 수량 요약 가독성 개선</t>
+        </is>
+      </c>
+      <c r="E2087" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2087" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2088" s="15" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="C2088" s="15" t="inlineStr">
+        <is>
+          <t>df9f279d</t>
+        </is>
+      </c>
+      <c r="D2088" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16 approval: 창고와 생산부 결재 권한 분리</t>
+        </is>
+      </c>
+      <c r="E2088" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2088" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2089" s="7" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="C2089" s="7" t="inlineStr">
+        <is>
+          <t>da9b1001</t>
+        </is>
+      </c>
+      <c r="D2089" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16 io: 창고 직원의 혼합 공정 요청을 생산부 결재로 연결</t>
+        </is>
+      </c>
+      <c r="E2089" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2089" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2090" s="15" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="C2090" s="15" t="inlineStr">
+        <is>
+          <t>17304d93</t>
+        </is>
+      </c>
+      <c r="D2090" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16 frontend: PC와 모바일 자동 승인 안내를 독립 결재 역할에 맞춤</t>
+        </is>
+      </c>
+      <c r="E2090" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2090" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2091" s="7" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="C2091" s="7" t="inlineStr">
+        <is>
+          <t>838e1329</t>
+        </is>
+      </c>
+      <c r="D2091" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16 docs: 생산부 전체 공정 결재 정책과 권한 검증 근거 기록</t>
+        </is>
+      </c>
+      <c r="E2091" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F2091" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2092" s="15" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="C2092" s="15" t="inlineStr">
+        <is>
+          <t>29583972</t>
+        </is>
+      </c>
+      <c r="D2092" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-16 inventory: 창고 격리 재고의 정상 복귀 위치 수정</t>
+        </is>
+      </c>
+      <c r="E2092" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2092" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2093" s="7" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C2093" s="7" t="inlineStr">
+        <is>
+          <t>58dca032</t>
+        </is>
+      </c>
+      <c r="D2093" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-19 history: 초기 재고 등록 작업명·경로와 자동 메모 표시 수정</t>
+        </is>
+      </c>
+      <c r="E2093" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2093" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2094" s="15" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="C2094" s="15" t="inlineStr">
+        <is>
+          <t>f4f9d8d3</t>
+        </is>
+      </c>
+      <c r="D2094" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-19 frontend: 대시보드 품목명 복사 버튼 추가</t>
+        </is>
+      </c>
+      <c r="E2094" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2094" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2095" s="19" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="C2095" s="19" t="inlineStr">
+        <is>
+          <t>e01d34a3</t>
+        </is>
+      </c>
+      <c r="D2095" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 search: 쉼표 OR 품목 검색 지원</t>
+        </is>
+      </c>
+      <c r="E2095" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2095" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2096" s="19" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="C2096" s="19" t="inlineStr">
+        <is>
+          <t>fd12e4f5</t>
+        </is>
+      </c>
+      <c r="D2096" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 직접 처리 로그의 창고 출처 판별 보완</t>
+        </is>
+      </c>
+      <c r="E2096" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2096" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2097" s="19" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="C2097" s="19" t="inlineStr">
+        <is>
+          <t>4ba69263</t>
+        </is>
+      </c>
+      <c r="D2097" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 최초 분류 필터와 분류별 전체 수량 제공</t>
+        </is>
+      </c>
+      <c r="E2097" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2097" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2098" s="19" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="C2098" s="19" t="inlineStr">
+        <is>
+          <t>b597b263</t>
+        </is>
+      </c>
+      <c r="D2098" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 품목과 시간대별 분류 수량 제공</t>
+        </is>
+      </c>
+      <c r="E2098" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2098" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2099" s="19" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="C2099" s="19" t="inlineStr">
+        <is>
+          <t>7697b19a</t>
+        </is>
+      </c>
+      <c r="D2099" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 발생 현황 요약과 비교 기준 접기</t>
+        </is>
+      </c>
+      <c r="E2099" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2099" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2100" s="19" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="C2100" s="19" t="inlineStr">
+        <is>
+          <t>5dd3f4d6</t>
+        </is>
+      </c>
+      <c r="D2100" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 통계 패널 반응형 배치 개선</t>
+        </is>
+      </c>
+      <c r="E2100" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2100" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2101" s="19" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="C2101" s="19" t="inlineStr">
+        <is>
+          <t>4c985698</t>
+        </is>
+      </c>
+      <c r="D2101" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 통계 필터를 발생 현황 아래로 이동</t>
+        </is>
+      </c>
+      <c r="E2101" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2101" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2102" s="19" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="C2102" s="19" t="inlineStr">
+        <is>
+          <t>48ad74d2</t>
+        </is>
+      </c>
+      <c r="D2102" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 조회 기간 중앙 정렬과 날짜 표시 개선</t>
+        </is>
+      </c>
+      <c r="E2102" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2102" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2103" s="19" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="C2103" s="19" t="inlineStr">
+        <is>
+          <t>16c5efe7</t>
+        </is>
+      </c>
+      <c r="D2103" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 현재 기간 이동 문구와 비활성 상태 개선</t>
+        </is>
+      </c>
+      <c r="E2103" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2103" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2104" s="19" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="C2104" s="19" t="inlineStr">
+        <is>
+          <t>2dc1f9e4</t>
+        </is>
+      </c>
+      <c r="D2104" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 분류 조회와 누적 그래프 및 품목 수량 표시</t>
+        </is>
+      </c>
+      <c r="E2104" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2104" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2105" s="19" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="C2105" s="19" t="inlineStr">
+        <is>
+          <t>311fcbb8</t>
+        </is>
+      </c>
+      <c r="D2105" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 가용재고 없는 품목 신규 선택 차단</t>
+        </is>
+      </c>
+      <c r="E2105" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2105" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2106" s="19" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="C2106" s="19" t="inlineStr">
+        <is>
+          <t>b51746c7</t>
+        </is>
+      </c>
+      <c r="D2106" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 기타 사유 메모 안내와 오류 통일</t>
+        </is>
+      </c>
+      <c r="E2106" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2106" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2107" s="19" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C2107" s="19" t="inlineStr">
+        <is>
+          <t>b1c35c89</t>
+        </is>
+      </c>
+      <c r="D2107" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 목록 정렬을 선택 칩으로 변경</t>
+        </is>
+      </c>
+      <c r="E2107" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2107" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2108" s="19" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="C2108" s="19" t="inlineStr">
+        <is>
+          <t>6434c755</t>
+        </is>
+      </c>
+      <c r="D2108" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 입력과 재가공의 수량 요약 통일</t>
+        </is>
+      </c>
+      <c r="E2108" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2108" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2109" s="19" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="C2109" s="19" t="inlineStr">
+        <is>
+          <t>085888ab</t>
+        </is>
+      </c>
+      <c r="D2109" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 처리 수량 요약과 입력 위치 개선</t>
+        </is>
+      </c>
+      <c r="E2109" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2109" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2110" s="19" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="C2110" s="19" t="inlineStr">
+        <is>
+          <t>ddd2481a</t>
+        </is>
+      </c>
+      <c r="D2110" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 처리 단계바와 후속 단계 표시 개선</t>
+        </is>
+      </c>
+      <c r="E2110" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2110" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2111" s="19" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="C2111" s="19" t="inlineStr">
+        <is>
+          <t>1f003911</t>
+        </is>
+      </c>
+      <c r="D2111" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 작업 선택 화면 가독성 개선</t>
+        </is>
+      </c>
+      <c r="E2111" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2111" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2112" s="19" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="C2112" s="19" t="inlineStr">
+        <is>
+          <t>2375f859</t>
+        </is>
+      </c>
+      <c r="D2112" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 defect: 사유 분류 펼침 전환 개선</t>
+        </is>
+      </c>
+      <c r="E2112" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2112" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2113" s="19" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="C2113" s="19" t="inlineStr">
+        <is>
+          <t>2dadfd7c</t>
+        </is>
+      </c>
+      <c r="D2113" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 공통 목록 스크롤과 마스터 스타일 기반 추가</t>
+        </is>
+      </c>
+      <c r="E2113" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2113" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2114" s="19" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="C2114" s="19" t="inlineStr">
+        <is>
+          <t>7c4bc9da</t>
+        </is>
+      </c>
+      <c r="D2114" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 모델 목록과 기본 정보 편집 배치 개선</t>
+        </is>
+      </c>
+      <c r="E2114" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2114" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2115" s="19" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="C2115" s="19" t="inlineStr">
+        <is>
+          <t>5333066b</t>
+        </is>
+      </c>
+      <c r="D2115" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 모델 연결 품목 미리보기 스크롤 개선</t>
+        </is>
+      </c>
+      <c r="E2115" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2115" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2116" s="19" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="C2116" s="19" t="inlineStr">
+        <is>
+          <t>f88dde17</t>
+        </is>
+      </c>
+      <c r="D2116" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 품목 목록 표와 상세 조작 크기 개선</t>
+        </is>
+      </c>
+      <c r="E2116" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2116" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2117" s="19" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="C2117" s="19" t="inlineStr">
+        <is>
+          <t>c92f78bf</t>
+        </is>
+      </c>
+      <c r="D2117" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 직원 목록과 권한 편집 배치 개선</t>
+        </is>
+      </c>
+      <c r="E2117" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2117" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2118" s="19" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="C2118" s="19" t="inlineStr">
+        <is>
+          <t>9c6377c8</t>
+        </is>
+      </c>
+      <c r="D2118" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 직원 초성 및 복합 검색 지원</t>
+        </is>
+      </c>
+      <c r="E2118" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2118" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2119" s="19" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="C2119" s="19" t="inlineStr">
+        <is>
+          <t>372b9ec4</t>
+        </is>
+      </c>
+      <c r="D2119" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 부서 목록과 상세 편집 카드 개선</t>
+        </is>
+      </c>
+      <c r="E2119" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2119" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2120" s="19" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="C2120" s="19" t="inlineStr">
+        <is>
+          <t>c90b4318</t>
+        </is>
+      </c>
+      <c r="D2120" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 품목 카테고리를 부서와 공정 단계로 선택</t>
+        </is>
+      </c>
+      <c r="E2120" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2120" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2121" s="19" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="C2121" s="19" t="inlineStr">
+        <is>
+          <t>d70b6ea6</t>
+        </is>
+      </c>
+      <c r="D2121" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 품목 입력과 재고 구매 필드 크기 통일</t>
+        </is>
+      </c>
+      <c r="E2121" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2121" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2122" s="19" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="C2122" s="19" t="inlineStr">
+        <is>
+          <t>482bf186</t>
+        </is>
+      </c>
+      <c r="D2122" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 사용 제품을 부서와 공정 단계 앞으로 이동</t>
+        </is>
+      </c>
+      <c r="E2122" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2122" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2123" s="19" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="C2123" s="19" t="inlineStr">
+        <is>
+          <t>60cf9382</t>
+        </is>
+      </c>
+      <c r="D2123" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 삭제 품목을 재고 상태 통계에서 분리</t>
+        </is>
+      </c>
+      <c r="E2123" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2123" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2124" s="19" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="C2124" s="19" t="inlineStr">
+        <is>
+          <t>ba6a49cd</t>
+        </is>
+      </c>
+      <c r="D2124" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 연간 공식 서식 내보내기 조작부 정리</t>
+        </is>
+      </c>
+      <c r="E2124" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2124" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2125" s="19" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="C2125" s="19" t="inlineStr">
+        <is>
+          <t>885a386d</t>
+        </is>
+      </c>
+      <c r="D2125" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 내보내기 유형과 설정 카드 재배치</t>
+        </is>
+      </c>
+      <c r="E2125" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2125" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2126" s="19" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="C2126" s="19" t="inlineStr">
+        <is>
+          <t>d167d341</t>
+        </is>
+      </c>
+      <c r="D2126" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 보안 PIN 변경 카드와 안내 이미지 정리</t>
+        </is>
+      </c>
+      <c r="E2126" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2126" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2127" s="19" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="C2127" s="19" t="inlineStr">
+        <is>
+          <t>935f2c0a</t>
+        </is>
+      </c>
+      <c r="D2127" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 정합성 검사 결과와 항목별 상태 표시 개선</t>
+        </is>
+      </c>
+      <c r="E2127" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2127" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2128" s="19" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="C2128" s="19" t="inlineStr">
+        <is>
+          <t>8bbf49fd</t>
+        </is>
+      </c>
+      <c r="D2128" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 최초 조회 상태와 공통 스켈레톤 기반 추가</t>
+        </is>
+      </c>
+      <c r="E2128" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2128" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2129" s="19" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="C2129" s="19" t="inlineStr">
+        <is>
+          <t>34918b2e</t>
+        </is>
+      </c>
+      <c r="D2129" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 모델 목록과 상세 스켈레톤 적용</t>
+        </is>
+      </c>
+      <c r="E2129" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2129" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2130" s="19" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="C2130" s="19" t="inlineStr">
+        <is>
+          <t>84ad0f22</t>
+        </is>
+      </c>
+      <c r="D2130" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 품목 목록과 상세 스켈레톤 적용</t>
+        </is>
+      </c>
+      <c r="E2130" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2130" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2131" s="19" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="C2131" s="19" t="inlineStr">
+        <is>
+          <t>8dd7a5d7</t>
+        </is>
+      </c>
+      <c r="D2131" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 직원 목록과 상세 스켈레톤 적용</t>
+        </is>
+      </c>
+      <c r="E2131" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2131" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2132" s="19" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="C2132" s="19" t="inlineStr">
+        <is>
+          <t>66360629</t>
+        </is>
+      </c>
+      <c r="D2132" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 부서 목록과 상세 스켈레톤 적용</t>
+        </is>
+      </c>
+      <c r="E2132" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2132" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2133" s="19" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="C2133" s="19" t="inlineStr">
+        <is>
+          <t>ec3e6fa6</t>
+        </is>
+      </c>
+      <c r="D2133" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 bom: 조회 스켈레톤과 늦은 응답 방어 적용</t>
+        </is>
+      </c>
+      <c r="E2133" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2133" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2134" s="19" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="C2134" s="19" t="inlineStr">
+        <is>
+          <t>09a4fe1a</t>
+        </is>
+      </c>
+      <c r="D2134" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 재고 거래 원본 조회 스켈레톤과 재시도 추가</t>
+        </is>
+      </c>
+      <c r="E2134" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2134" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2135" s="19" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="C2135" s="19" t="inlineStr">
+        <is>
+          <t>023864be</t>
+        </is>
+      </c>
+      <c r="D2135" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 작업 감사 파일 조회 스켈레톤과 재시도 추가</t>
+        </is>
+      </c>
+      <c r="E2135" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2135" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2136" s="19" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="C2136" s="19" t="inlineStr">
+        <is>
+          <t>728e8f65</t>
+        </is>
+      </c>
+      <c r="D2136" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 정합성 초기 조회 표시 보완</t>
+        </is>
+      </c>
+      <c r="E2136" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2136" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2137" s="19" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C2137" s="19" t="inlineStr">
+        <is>
+          <t>74a5de77</t>
+        </is>
+      </c>
+      <c r="D2137" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 bom: 부서 필터 이동과 선택 품목 헤더 확장</t>
+        </is>
+      </c>
+      <c r="E2137" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2137" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2138" s="19" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="C2138" s="19" t="inlineStr">
+        <is>
+          <t>846458aa</t>
+        </is>
+      </c>
+      <c r="D2138" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 bom: 미배치 원자재 패널 배치와 접근성 개선</t>
+        </is>
+      </c>
+      <c r="E2138" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2138" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2139" s="19" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="C2139" s="19" t="inlineStr">
+        <is>
+          <t>b39b7e31</t>
+        </is>
+      </c>
+      <c r="D2139" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 공통 페이드와 상세 선택 전환 적용</t>
+        </is>
+      </c>
+      <c r="E2139" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2139" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2140" s="19" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="C2140" s="19" t="inlineStr">
+        <is>
+          <t>f91b7164</t>
+        </is>
+      </c>
+      <c r="D2140" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 품목 상세 내부 탭 페이드와 중복 전환 방지</t>
+        </is>
+      </c>
+      <c r="E2140" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2140" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2141" s="19" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="C2141" s="19" t="inlineStr">
+        <is>
+          <t>3fbef326</t>
+        </is>
+      </c>
+      <c r="D2141" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 내보내기 내부 화면 전환 페이드 적용</t>
+        </is>
+      </c>
+      <c r="E2141" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2141" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2142" s="19" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="C2142" s="19" t="inlineStr">
+        <is>
+          <t>81f120dd</t>
+        </is>
+      </c>
+      <c r="D2142" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 bom: 편집과 사용처 및 미배치 패널 전환 페이드 적용</t>
+        </is>
+      </c>
+      <c r="E2142" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2142" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2143" s="19" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="C2143" s="19" t="inlineStr">
+        <is>
+          <t>4004199c</t>
+        </is>
+      </c>
+      <c r="D2143" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 bom: 툴팁 측정을 표시 시점으로 지연</t>
+        </is>
+      </c>
+      <c r="E2143" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2143" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2144" s="19" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="C2144" s="19" t="inlineStr">
+        <is>
+          <t>63df8147</t>
+        </is>
+      </c>
+      <c r="D2144" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 화면 밖 품목 행 그리기 비용 축소</t>
+        </is>
+      </c>
+      <c r="E2144" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2144" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2145" s="19" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="C2145" s="19" t="inlineStr">
+        <is>
+          <t>e6530060</t>
+        </is>
+      </c>
+      <c r="D2145" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 bom: 화면 밖 목록 행 그리기 비용 축소</t>
+        </is>
+      </c>
+      <c r="E2145" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2145" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2146" s="19" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="C2146" s="19" t="inlineStr">
+        <is>
+          <t>ca4db166</t>
+        </is>
+      </c>
+      <c r="D2146" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 품목과 BOM 진입 틀을 본문보다 먼저 표시 및 번들 예산 동기화</t>
+        </is>
+      </c>
+      <c r="E2146" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2146" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2147" s="19" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="C2147" s="19" t="inlineStr">
+        <is>
+          <t>07444d51</t>
+        </is>
+      </c>
+      <c r="D2147" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 frontend: 메뉴 권한 회수 시 작성 내용 보존</t>
+        </is>
+      </c>
+      <c r="E2147" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2147" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2148" s="19" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="C2148" s="19" t="inlineStr">
+        <is>
+          <t>e4195ad3</t>
+        </is>
+      </c>
+      <c r="D2148" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 frontend: 승인함 권한 회수 시 진행 중 결재 보존</t>
+        </is>
+      </c>
+      <c r="E2148" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2148" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2149" s="19" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="C2149" s="19" t="inlineStr">
+        <is>
+          <t>92058aa7</t>
+        </is>
+      </c>
+      <c r="D2149" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 frontend: 로그인 직원 권한 실시간 동기화</t>
+        </is>
+      </c>
+      <c r="E2149" s="19" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2149" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2150" s="19" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="C2150" s="19" t="inlineStr">
+        <is>
+          <t>1efd0228</t>
+        </is>
+      </c>
+      <c r="D2150" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 admin: 본인 직원 권한 저장 결과 즉시 반영 및 안내 문서 동기화</t>
+        </is>
+      </c>
+      <c r="E2150" s="19" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2150" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2151" s="19" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="C2151" s="19" t="inlineStr">
+        <is>
+          <t>49ad542d</t>
+        </is>
+      </c>
+      <c r="D2151" s="20" t="inlineStr">
+        <is>
+          <t>Merge branch 'codex/mes-3016-feature-split-20261019' into codex/mes-3016-main-integration-20261019</t>
+        </is>
+      </c>
+      <c r="E2151" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2151" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2152" s="19" t="inlineStr">
+        <is>
+          <t>22:09</t>
+        </is>
+      </c>
+      <c r="C2152" s="19" t="inlineStr">
+        <is>
+          <t>9824903e</t>
+        </is>
+      </c>
+      <c r="D2152" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-19 ops: 빈 SQLite WAL 파일의 백업 변경 오탐 수정</t>
+        </is>
+      </c>
+      <c r="E2152" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2152" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2153" s="7" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="C2153" s="7" t="inlineStr">
+        <is>
+          <t>2516f8e4</t>
+        </is>
+      </c>
+      <c r="D2153" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20 backend: 실사 잘못된 커서 테스트에 검색 설정 버전 반영</t>
+        </is>
+      </c>
+      <c r="E2153" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2153" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2154" s="15" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="C2154" s="15" t="inlineStr">
+        <is>
+          <t>d2b9f453</t>
+        </is>
+      </c>
+      <c r="D2154" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-20 defect: 불량 목록 정렬 칩 테스트 기대값 갱신</t>
+        </is>
+      </c>
+      <c r="E2154" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2154" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2155" s="7" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="C2155" s="7" t="inlineStr">
+        <is>
+          <t>0c8725d1</t>
+        </is>
+      </c>
+      <c r="D2155" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20 frontend: 전체화면 테스트의 권한 회수 훅 모의 보완</t>
+        </is>
+      </c>
+      <c r="E2155" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2155" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2156" s="15" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="C2156" s="15" t="inlineStr">
+        <is>
+          <t>22abe83c</t>
+        </is>
+      </c>
+      <c r="D2156" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-20 history: 조합 중 즉시 검색 테스트 계약 갱신</t>
+        </is>
+      </c>
+      <c r="E2156" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2156" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2157" s="7" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="C2157" s="7" t="inlineStr">
+        <is>
+          <t>18fc7e2d</t>
+        </is>
+      </c>
+      <c r="D2157" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20 defect: E2E 불량 단계 이동과 필터 동선 갱신</t>
+        </is>
+      </c>
+      <c r="E2157" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2157" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2158" s="15" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="C2158" s="15" t="inlineStr">
+        <is>
+          <t>5ff9e8a7</t>
+        </is>
+      </c>
+      <c r="D2158" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-20 frontend: 모바일 E2E 검색을 접근성 영역으로 선택</t>
+        </is>
+      </c>
+      <c r="E2158" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2158" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2159" s="7" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C2159" s="7" t="inlineStr">
+        <is>
+          <t>e55918bc</t>
+        </is>
+      </c>
+      <c r="D2159" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20 frontend: 최근 내역 배지와 입출고·불량 화면 높이 및 간격 통일</t>
+        </is>
+      </c>
+      <c r="E2159" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2159" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2160" s="15" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="C2160" s="15" t="inlineStr">
+        <is>
+          <t>62ab7305</t>
+        </is>
+      </c>
+      <c r="D2160" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-20 frontend: 재고 선택 해제와 등록된 검색어 연결 검색 및 편집 초기화 개선</t>
+        </is>
+      </c>
+      <c r="E2160" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2160" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2161" s="7" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="C2161" s="7" t="inlineStr">
+        <is>
+          <t>81b5875d</t>
+        </is>
+      </c>
+      <c r="D2161" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20 frontend: 전수조사 대기 화면 가독성과 전체 높이 배치 개선</t>
+        </is>
+      </c>
+      <c r="E2161" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2161" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2162" s="15" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="C2162" s="15" t="inlineStr">
+        <is>
+          <t>5de9a8ea</t>
+        </is>
+      </c>
+      <c r="D2162" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-20 frontend: 입출고 방향별 색상을 PC와 모바일 전체 단계에 통일</t>
+        </is>
+      </c>
+      <c r="E2162" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2162" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2163" s="7" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="C2163" s="7" t="inlineStr">
+        <is>
+          <t>716ea6e5</t>
+        </is>
+      </c>
+      <c r="D2163" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-20 frontend: 대시보드 표 헤더 색 잘림과 사이드바 로고 누락 수정</t>
+        </is>
+      </c>
+      <c r="E2163" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2163" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2164" s="15" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="C2164" s="15" t="inlineStr">
+        <is>
+          <t>238763db</t>
+        </is>
+      </c>
+      <c r="D2164" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-21 workflow: 논리적 단위별 커밋과 이력 재구성 규칙 명시</t>
+        </is>
+      </c>
+      <c r="E2164" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2164" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2165" s="7" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="C2165" s="7" t="inlineStr">
+        <is>
+          <t>5d6617a0</t>
+        </is>
+      </c>
+      <c r="D2165" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21 admin: 공통 전환 효과와 목록 렌더링 기반 개선</t>
+        </is>
+      </c>
+      <c r="E2165" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2165" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2166" s="15" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="C2166" s="15" t="inlineStr">
+        <is>
+          <t>c707b7f8</t>
+        </is>
+      </c>
+      <c r="D2166" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-21 admin: 조회 캐시와 저장 중복 및 늦은 응답 보호</t>
+        </is>
+      </c>
+      <c r="E2166" s="15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2166" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2167" s="7" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="C2167" s="7" t="inlineStr">
+        <is>
+          <t>d487abab</t>
+        </is>
+      </c>
+      <c r="D2167" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21 admin: 모델 직원 부서 선택과 미저장 입력 보호</t>
+        </is>
+      </c>
+      <c r="E2167" s="7" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2167" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2168" s="15" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="C2168" s="15" t="inlineStr">
+        <is>
+          <t>07a45d63</t>
+        </is>
+      </c>
+      <c r="D2168" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-21 items: 상세 입력 보호와 목록 상태 복원</t>
+        </is>
+      </c>
+      <c r="E2168" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2168" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2169" s="7" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="C2169" s="7" t="inlineStr">
+        <is>
+          <t>e5f0da66</t>
+        </is>
+      </c>
+      <c r="D2169" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21 bom: 로딩 배치 정렬과 목록 전환 성능 개선</t>
+        </is>
+      </c>
+      <c r="E2169" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2169" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2170" s="15" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="C2170" s="15" t="inlineStr">
+        <is>
+          <t>ec45b91a</t>
+        </is>
+      </c>
+      <c r="D2170" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-21 admin: 브라우저 회귀 검사와 완료 검증 기록</t>
+        </is>
+      </c>
+      <c r="E2170" s="15" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="F2170" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2171" s="7" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="C2171" s="7" t="inlineStr">
+        <is>
+          <t>48bdf78c</t>
+        </is>
+      </c>
+      <c r="D2171" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21 inventory: 작업 예약과 가용 재고 및 관리자 관리 기능 추가</t>
+        </is>
+      </c>
+      <c r="E2171" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2171" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2172" s="15" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="C2172" s="15" t="inlineStr">
+        <is>
+          <t>efaea246</t>
+        </is>
+      </c>
+      <c r="D2172" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-21 docs: 작업 예약 계약과 디자인 및 검증 결과 기록</t>
+        </is>
+      </c>
+      <c r="E2172" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F2172" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2173" s="7" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="C2173" s="7" t="inlineStr">
+        <is>
+          <t>ca9eab0c</t>
+        </is>
+      </c>
+      <c r="D2173" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21 revert: 작업 예약 기능 통합 이전 상태로 복원</t>
+        </is>
+      </c>
+      <c r="E2173" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2173" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2174" s="15" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="C2174" s="15" t="inlineStr">
+        <is>
+          <t>57767831</t>
+        </is>
+      </c>
+      <c r="D2174" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-21 history: 출하 예약으로 인한 취소 제한 안내 개선</t>
+        </is>
+      </c>
+      <c r="E2174" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2174" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2175" s="7" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C2175" s="7" t="inlineStr">
+        <is>
+          <t>541f7be4</t>
+        </is>
+      </c>
+      <c r="D2175" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21 frontend: 입출고 내역 품목명 복사 버튼 추가 및 정렬</t>
+        </is>
+      </c>
+      <c r="E2175" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2175" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2176" s="15" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C2176" s="15" t="inlineStr">
+        <is>
+          <t>6b78f904</t>
+        </is>
+      </c>
+      <c r="D2176" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-21 frontend: 입출고 내역 검색창 입력 시 높이 변화 수정</t>
+        </is>
+      </c>
+      <c r="E2176" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2176" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2177" s="7" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C2177" s="7" t="inlineStr">
+        <is>
+          <t>5c2f5e0d</t>
+        </is>
+      </c>
+      <c r="D2177" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-21 frontend: 입출고 건수 배지 크기와 중앙 정렬 개선</t>
+        </is>
+      </c>
+      <c r="E2177" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2177" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2178" s="15" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="C2178" s="15" t="inlineStr">
+        <is>
+          <t>46d15d6d</t>
+        </is>
+      </c>
+      <c r="D2178" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-22 backend: 승인된 입출고 작업의 요청자 취소 권한 수정</t>
+        </is>
+      </c>
+      <c r="E2178" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2178" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2179" s="7" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="C2179" s="7" t="inlineStr">
+        <is>
+          <t>c33d621b</t>
+        </is>
+      </c>
+      <c r="D2179" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-22 frontend: BOM 잠금 안내와 검색창 스켈레톤 배치 정렬</t>
+        </is>
+      </c>
+      <c r="E2179" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2179" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2180" s="15" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="C2180" s="15" t="inlineStr">
+        <is>
+          <t>4ffaaf46</t>
+        </is>
+      </c>
+      <c r="D2180" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-22 frontend: 대시보드 검색창과 스크롤 스켈레톤 정합성 개선</t>
+        </is>
+      </c>
+      <c r="E2180" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2180" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2181" s="19" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="C2181" s="19" t="inlineStr">
+        <is>
+          <t>8b886761</t>
+        </is>
+      </c>
+      <c r="D2181" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-22 mes: 작업 예약과 공유 작업 현황 및 상세 화면 통합</t>
+        </is>
+      </c>
+      <c r="E2181" s="19" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2181" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" s="19" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2182" s="19" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="C2182" s="19" t="inlineStr">
+        <is>
+          <t>263264a2</t>
+        </is>
+      </c>
+      <c r="D2182" s="20" t="inlineStr">
+        <is>
+          <t>2026-10-22 docs: 메인 예약 전환과 재기동 검증 기록</t>
+        </is>
+      </c>
+      <c r="E2182" s="19" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F2182" s="21" t="inlineStr">
+        <is>
+          <t>근무 외</t>
+        </is>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2183" s="7" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="C2183" s="7" t="inlineStr">
+        <is>
+          <t>67c42305</t>
+        </is>
+      </c>
+      <c r="D2183" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23 frontend: 대시보드 스켈레톤 스크롤 높이를 실제 목록과 동기화</t>
+        </is>
+      </c>
+      <c r="E2183" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2183" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/_attic/docs/개발현황.xlsx
+++ b/_attic/docs/개발현황.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2182건 (회사 기간 670건)</t>
+          <t>2208건 (회사 기간 670건)</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>112 / 121개 (93%)</t>
+          <t>113 / 122개 (93%)</t>
         </is>
       </c>
     </row>
@@ -4590,14 +4590,14 @@
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t>■</t>
+            <t>■■■■■■■■■■■■■</t>
           </r>
           <r>
             <rPr>
               <color rgb="00000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">  (1)</t>
+            <t xml:space="preserve">  (27)</t>
           </r>
         </is>
       </c>
@@ -5382,7 +5382,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" ht="113.4" customHeight="1">
+    <row r="26" ht="162" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
           <t>2026-10-19 ~ 10-23</t>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>불량·관리·작업 예약 개선</t>
+          <t>불량·예약·실사·출하 개선</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -5401,11 +5401,14 @@
 품목 검색과 입출고 내역 확인 편의 개선
 컴퓨터·모바일 입출고 방향 안내와 취소 처리 개선
 작업 예약·공유 작업 현황 및 상세 확인 추가
-전수조사 대기 화면과 로그인 로고 표시 개선</t>
+전수조사 중 기존 작업 보존·예약 해제와 조사 반영 후 이어하기
+출하 작업자 입력과 전체 작업 확인 통합
+부족 자재의 확보 가능 수량 예약과 제출 제한 보완 진행 중
+로그인 로고 표시 개선</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -5419,7 +5422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8173,27 +8176,27 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="12" t="n">
+      <c r="A114" s="9" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="13" t="inlineStr">
-        <is>
-          <t>실 재고 데이터 입력 + 직원 테스트</t>
-        </is>
-      </c>
-      <c r="C114" s="12" t="inlineStr">
-        <is>
-          <t>데이터</t>
-        </is>
-      </c>
-      <c r="D114" s="14" t="inlineStr">
-        <is>
-          <t>🔲 예정</t>
-        </is>
-      </c>
-      <c r="E114" s="13" t="inlineStr">
-        <is>
-          <t>BOM·입출고 정리 후</t>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>전수조사 중 작업 일시중지·재개</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>재고</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>✅ 완료</t>
+        </is>
+      </c>
+      <c r="E114" s="10" t="inlineStr">
+        <is>
+          <t>기존 작업·수량을 보존하고 예약 해제 후 조사 반영 시 이어하기</t>
         </is>
       </c>
     </row>
@@ -8203,12 +8206,12 @@
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>불량 처리 흐름 Phase 2</t>
+          <t>실 재고 데이터 입력 + 직원 테스트</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>데이터</t>
         </is>
       </c>
       <c r="D115" s="14" t="inlineStr">
@@ -8218,7 +8221,7 @@
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>부서 결재·집계·자동화</t>
+          <t>BOM·입출고 정리 후</t>
         </is>
       </c>
     </row>
@@ -8228,12 +8231,12 @@
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>역할별 접근 권한 연동</t>
+          <t>불량 처리 흐름 Phase 2</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>보안</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr">
@@ -8243,7 +8246,7 @@
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>부서·역할 기반 (PIN 로그인 완료)</t>
+          <t>부서 결재·집계·자동화</t>
         </is>
       </c>
     </row>
@@ -8253,12 +8256,12 @@
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>총재고 / 가용재고 / 예약재고 분리</t>
+          <t>역할별 접근 권한 연동</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>재고</t>
+          <t>보안</t>
         </is>
       </c>
       <c r="D117" s="14" t="inlineStr">
@@ -8268,7 +8271,7 @@
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>재고 가용성 계산 고도화</t>
+          <t>부서·역할 기반 (PIN 로그인 완료)</t>
         </is>
       </c>
     </row>
@@ -8278,12 +8281,12 @@
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>외부 접근 환경 구성</t>
+          <t>총재고 / 가용재고 / 예약재고 분리</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>인프라</t>
+          <t>재고</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
@@ -8293,7 +8296,7 @@
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>PC 또는 NAS 서버 + API 인증</t>
+          <t>재고 가용성 계산 고도화</t>
         </is>
       </c>
     </row>
@@ -8303,12 +8306,12 @@
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>발주 관리</t>
+          <t>외부 접근 환경 구성</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>인프라</t>
         </is>
       </c>
       <c r="D119" s="14" t="inlineStr">
@@ -8316,7 +8319,11 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E119" s="13" t="inlineStr"/>
+      <c r="E119" s="13" t="inlineStr">
+        <is>
+          <t>PC 또는 NAS 서버 + API 인증</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="12" t="n">
@@ -8324,12 +8331,12 @@
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>생산 실적 / 원가 관리</t>
+          <t>발주 관리</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
@@ -8345,12 +8352,12 @@
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>부서별 생산진행도 대시보드</t>
+          <t>생산 실적 / 원가 관리</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>관리</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
@@ -8358,11 +8365,7 @@
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E121" s="13" t="inlineStr">
-        <is>
-          <t>사장님 요청 — 검토 중</t>
-        </is>
-      </c>
+      <c r="E121" s="13" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="n">
@@ -8370,20 +8373,45 @@
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
+          <t>부서별 생산진행도 대시보드</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>관리</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="inlineStr">
+        <is>
+          <t>🔲 예정</t>
+        </is>
+      </c>
+      <c r="E122" s="13" t="inlineStr">
+        <is>
+          <t>사장님 요청 — 검토 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="13" t="inlineStr">
+        <is>
           <t>출하 거래처 관리</t>
         </is>
       </c>
-      <c r="C122" s="12" t="inlineStr">
+      <c r="C123" s="12" t="inlineStr">
         <is>
           <t>출하</t>
         </is>
       </c>
-      <c r="D122" s="14" t="inlineStr">
+      <c r="D123" s="14" t="inlineStr">
         <is>
           <t>🔲 예정</t>
         </is>
       </c>
-      <c r="E122" s="13" t="inlineStr">
+      <c r="E123" s="13" t="inlineStr">
         <is>
           <t>거래처 마스터 + 출하 이력</t>
         </is>
@@ -11609,18 +11637,22 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="27" customHeight="1">
+    <row r="136" ht="67.5" customHeight="1">
       <c r="A136" s="15" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
       <c r="B136" s="15" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C136" s="16" t="inlineStr">
         <is>
-          <t>2026-10-23 frontend: 대시보드 스켈레톤 스크롤 높이를 실제 목록과 동기화</t>
+          <t>2026-10-23 frontend: 대시보드 스켈레톤 스크롤 높이를 실제 목록과 동기화
+2026-10-23 frontend: 일보 불량 재작업 상세 표시 수정
+2026-10-23 frontend: 일보 상세 펼침 시 작업 내역 높이 유지
+2026-10-23 backend: 재제출 이전 취소 이력을 승인 완료 집계에서 제외
+2026-10-23 backend: 과거 일부 완료 작업의 안전한 상태 정정 도구 추가</t>
         </is>
       </c>
       <c r="D136" s="15" t="inlineStr">
@@ -11640,7 +11672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2183"/>
+  <dimension ref="A1:F2209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -81507,6 +81539,838 @@
         </is>
       </c>
     </row>
+    <row r="2184">
+      <c r="A2184" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2184" s="15" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="C2184" s="15" t="inlineStr">
+        <is>
+          <t>e9a4374e</t>
+        </is>
+      </c>
+      <c r="D2184" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23 frontend: 일보 불량 재작업 상세 표시 수정</t>
+        </is>
+      </c>
+      <c r="E2184" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2184" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2185" s="7" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="C2185" s="7" t="inlineStr">
+        <is>
+          <t>adc33780</t>
+        </is>
+      </c>
+      <c r="D2185" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23 frontend: 일보 상세 펼침 시 작업 내역 높이 유지</t>
+        </is>
+      </c>
+      <c r="E2185" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2185" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2186" s="15" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="C2186" s="15" t="inlineStr">
+        <is>
+          <t>33f862f0</t>
+        </is>
+      </c>
+      <c r="D2186" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23 backend: 재제출 이전 취소 이력을 승인 완료 집계에서 제외</t>
+        </is>
+      </c>
+      <c r="E2186" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2186" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2187" s="7" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="C2187" s="7" t="inlineStr">
+        <is>
+          <t>26d7f1e6</t>
+        </is>
+      </c>
+      <c r="D2187" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23 backend: 과거 일부 완료 작업의 안전한 상태 정정 도구 추가</t>
+        </is>
+      </c>
+      <c r="E2187" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2187" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2188" s="15" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="C2188" s="15" t="inlineStr">
+        <is>
+          <t>c7fe0dc1</t>
+        </is>
+      </c>
+      <c r="D2188" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23 frontend: 대시보드와 상세 수량 갱신 동기화</t>
+        </is>
+      </c>
+      <c r="E2188" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2188" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2189" s="7" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="C2189" s="7" t="inlineStr">
+        <is>
+          <t>0dcffb88</t>
+        </is>
+      </c>
+      <c r="D2189" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23 frontend: 로그인 로고 로딩과 모바일 배치 개선</t>
+        </is>
+      </c>
+      <c r="E2189" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2189" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2190" s="15" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="C2190" s="15" t="inlineStr">
+        <is>
+          <t>b5a7b852</t>
+        </is>
+      </c>
+      <c r="D2190" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23 docs: 주간보고와 개발현황을 10월 23일 기준으로 갱신</t>
+        </is>
+      </c>
+      <c r="E2190" s="15" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F2190" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2191" s="7" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="C2191" s="7" t="inlineStr">
+        <is>
+          <t>f1f72c15</t>
+        </is>
+      </c>
+      <c r="D2191" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23 docs: 메인과 병합 후보 비교 검증 계획 추가</t>
+        </is>
+      </c>
+      <c r="E2191" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F2191" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2192" s="15" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="C2192" s="15" t="inlineStr">
+        <is>
+          <t>9a76c769</t>
+        </is>
+      </c>
+      <c r="D2192" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23 frontend: 전체 작업 기본 정렬을 부서순으로 변경</t>
+        </is>
+      </c>
+      <c r="E2192" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2192" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2193" s="7" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="C2193" s="7" t="inlineStr">
+        <is>
+          <t>29a849ec</t>
+        </is>
+      </c>
+      <c r="D2193" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23 warehouse: 입출고 메모 공유와 작업 목록 표시 정리</t>
+        </is>
+      </c>
+      <c r="E2193" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2193" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2194" s="15" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="C2194" s="15" t="inlineStr">
+        <is>
+          <t>3359b3a7</t>
+        </is>
+      </c>
+      <c r="D2194" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23 warehouse: 부서 결재 담당자의 전체 작업 기본 진입 적용</t>
+        </is>
+      </c>
+      <c r="E2194" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2194" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2195" s="7" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="C2195" s="7" t="inlineStr">
+        <is>
+          <t>56853ed9</t>
+        </is>
+      </c>
+      <c r="D2195" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23 warehouse: 예정 변동 배지를 한 줄로 통일</t>
+        </is>
+      </c>
+      <c r="E2195" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2195" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2196" s="15" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="C2196" s="15" t="inlineStr">
+        <is>
+          <t>b10b3d69</t>
+        </is>
+      </c>
+      <c r="D2196" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23 backend: 저장 작업 건수와 단건 조회 및 일괄 읽기 최적화</t>
+        </is>
+      </c>
+      <c r="E2196" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2196" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2197" s="7" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="C2197" s="7" t="inlineStr">
+        <is>
+          <t>ae0007d1</t>
+        </is>
+      </c>
+      <c r="D2197" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23 frontend: 로그인 경계의 작업 캐시와 조회 정책 정리</t>
+        </is>
+      </c>
+      <c r="E2197" s="7" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2197" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2198" s="15" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="C2198" s="15" t="inlineStr">
+        <is>
+          <t>674274dd</t>
+        </is>
+      </c>
+      <c r="D2198" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23 warehouse: 작업 건수 분리와 최신 저장 작업 복원 적용</t>
+        </is>
+      </c>
+      <c r="E2198" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2198" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2199" s="7" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="C2199" s="7" t="inlineStr">
+        <is>
+          <t>03570757</t>
+        </is>
+      </c>
+      <c r="D2199" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23 backend: 전수조사 작업 일시중지 모델과 마이그레이션 추가</t>
+        </is>
+      </c>
+      <c r="E2199" s="7" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2199" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2200" s="15" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C2200" s="15" t="inlineStr">
+        <is>
+          <t>706019b4</t>
+        </is>
+      </c>
+      <c r="D2200" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23 backend: 전수조사 작업 예약 해제와 원자적 재개 구현</t>
+        </is>
+      </c>
+      <c r="E2200" s="15" t="inlineStr">
+        <is>
+          <t>backend</t>
+        </is>
+      </c>
+      <c r="F2200" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2201" s="7" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="C2201" s="7" t="inlineStr">
+        <is>
+          <t>d9278105</t>
+        </is>
+      </c>
+      <c r="D2201" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23 warehouse: 일시중지 상태와 예약 관리 이력 표시</t>
+        </is>
+      </c>
+      <c r="E2201" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2201" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2202" s="15" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="C2202" s="15" t="inlineStr">
+        <is>
+          <t>58748514</t>
+        </is>
+      </c>
+      <c r="D2202" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23 warehouse: 조사 반영 후 기존 수량으로 바로 작업 이어가기</t>
+        </is>
+      </c>
+      <c r="E2202" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2202" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2203" s="7" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="C2203" s="7" t="inlineStr">
+        <is>
+          <t>8efb0464</t>
+        </is>
+      </c>
+      <c r="D2203" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23 docs: 작업 일시중지 재개 정책과 검증 기록 정리</t>
+        </is>
+      </c>
+      <c r="E2203" s="7" t="inlineStr">
+        <is>
+          <t>docs</t>
+        </is>
+      </c>
+      <c r="F2203" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2204" s="15" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="C2204" s="15" t="inlineStr">
+        <is>
+          <t>7b990e43</t>
+        </is>
+      </c>
+      <c r="D2204" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23 warehouse: 튜닝 직원의 입출고 품목 전환 허용</t>
+        </is>
+      </c>
+      <c r="E2204" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2204" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2205" s="7" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="C2205" s="7" t="inlineStr">
+        <is>
+          <t>b1e85d8e</t>
+        </is>
+      </c>
+      <c r="D2205" s="8" t="inlineStr">
+        <is>
+          <t>Merge commit '8efb04648e0b9f2b795b2d0c149c2537bb9498d2' into HEAD</t>
+        </is>
+      </c>
+      <c r="E2205" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2205" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2206" s="15" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="C2206" s="15" t="inlineStr">
+        <is>
+          <t>6f9966e9</t>
+        </is>
+      </c>
+      <c r="D2206" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23 warehouse: 튜닝 직원 품목 전환 허용 롤백</t>
+        </is>
+      </c>
+      <c r="E2206" s="15" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2206" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2207" s="7" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="C2207" s="7" t="inlineStr">
+        <is>
+          <t>a28b4335</t>
+        </is>
+      </c>
+      <c r="D2207" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-23 shipping: 출하 작업자 입력과 전체 작업 통합</t>
+        </is>
+      </c>
+      <c r="E2207" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2207" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" s="15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2208" s="15" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="C2208" s="15" t="inlineStr">
+        <is>
+          <t>89752e5b</t>
+        </is>
+      </c>
+      <c r="D2208" s="16" t="inlineStr">
+        <is>
+          <t>2026-10-23 frontend: 출하 상세 진입 로딩과 요약 중앙 정렬 개선</t>
+        </is>
+      </c>
+      <c r="E2208" s="15" t="inlineStr">
+        <is>
+          <t>frontend</t>
+        </is>
+      </c>
+      <c r="F2208" s="15" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2209" s="7" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="C2209" s="7" t="inlineStr">
+        <is>
+          <t>5f62956b</t>
+        </is>
+      </c>
+      <c r="D2209" s="8" t="inlineStr">
+        <is>
+          <t>Merge branch 'main' into HEAD</t>
+        </is>
+      </c>
+      <c r="E2209" s="7" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F2209" s="7" t="inlineStr">
+        <is>
+          <t>근무</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
